--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -81,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -95,11 +95,14 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -129,6 +132,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -496,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5557,6 +5566,85 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n">
+        <v>4896</v>
+      </c>
+      <c r="C62" s="12" t="n">
+        <v>7984</v>
+      </c>
+      <c r="D62" s="12" t="n">
+        <v>4039</v>
+      </c>
+      <c r="E62" s="12" t="n">
+        <v>8023</v>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>4764</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>4168</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>8149</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>7908</v>
+      </c>
+      <c r="J62" s="12" t="n">
+        <v>3637</v>
+      </c>
+      <c r="K62" s="12" t="n">
+        <v>8637</v>
+      </c>
+      <c r="L62" s="12" t="n">
+        <v>3202</v>
+      </c>
+      <c r="M62" s="12" t="n">
+        <v>8201</v>
+      </c>
+      <c r="N62" s="12" t="n">
+        <v>3582</v>
+      </c>
+      <c r="O62" s="12" t="n">
+        <v>8038</v>
+      </c>
+      <c r="P62" s="12" t="n">
+        <v>2830</v>
+      </c>
+      <c r="Q62" s="12" t="n">
+        <v>2386</v>
+      </c>
+      <c r="R62" s="12" t="n">
+        <v>8059</v>
+      </c>
+      <c r="S62" s="12" t="n">
+        <v>4006</v>
+      </c>
+      <c r="T62" s="12" t="n">
+        <v>5148</v>
+      </c>
+      <c r="U62" s="12" t="n">
+        <v>5211</v>
+      </c>
+      <c r="V62" s="12" t="n">
+        <v>7515</v>
+      </c>
+      <c r="W62" s="12" t="n">
+        <v>4933</v>
+      </c>
+      <c r="X62" s="12" t="n">
+        <v>3332</v>
+      </c>
+      <c r="Y62" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -81,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -98,11 +98,14 @@
     <border>
       <left style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -138,6 +141,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -505,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y62"/>
+  <dimension ref="A1:Y63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5645,6 +5654,85 @@
         <v>0</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>4837</v>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>7699</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>3848</v>
+      </c>
+      <c r="E63" s="14" t="n">
+        <v>8075</v>
+      </c>
+      <c r="F63" s="14" t="n">
+        <v>4957</v>
+      </c>
+      <c r="G63" s="14" t="n">
+        <v>4289</v>
+      </c>
+      <c r="H63" s="14" t="n">
+        <v>7652</v>
+      </c>
+      <c r="I63" s="14" t="n">
+        <v>8108</v>
+      </c>
+      <c r="J63" s="14" t="n">
+        <v>3497</v>
+      </c>
+      <c r="K63" s="14" t="n">
+        <v>8124</v>
+      </c>
+      <c r="L63" s="14" t="n">
+        <v>3339</v>
+      </c>
+      <c r="M63" s="14" t="n">
+        <v>8322</v>
+      </c>
+      <c r="N63" s="14" t="n">
+        <v>3469</v>
+      </c>
+      <c r="O63" s="14" t="n">
+        <v>8143</v>
+      </c>
+      <c r="P63" s="14" t="n">
+        <v>2953</v>
+      </c>
+      <c r="Q63" s="14" t="n">
+        <v>2455</v>
+      </c>
+      <c r="R63" s="14" t="n">
+        <v>7789</v>
+      </c>
+      <c r="S63" s="14" t="n">
+        <v>4139</v>
+      </c>
+      <c r="T63" s="14" t="n">
+        <v>5186</v>
+      </c>
+      <c r="U63" s="14" t="n">
+        <v>5465</v>
+      </c>
+      <c r="V63" s="14" t="n">
+        <v>7548</v>
+      </c>
+      <c r="W63" s="14" t="n">
+        <v>4824</v>
+      </c>
+      <c r="X63" s="14" t="n">
+        <v>3446</v>
+      </c>
+      <c r="Y63" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y63"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5733,6 +5733,82 @@
         <v>0</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>5100</v>
+      </c>
+      <c r="C64" t="n">
+        <v>9100</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4100</v>
+      </c>
+      <c r="E64" t="n">
+        <v>17800</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4400</v>
+      </c>
+      <c r="H64" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I64" t="n">
+        <v>6600</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3700</v>
+      </c>
+      <c r="K64" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3200</v>
+      </c>
+      <c r="M64" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3600</v>
+      </c>
+      <c r="O64" t="n">
+        <v>8200</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2900</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R64" t="n">
+        <v>8700</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T64" t="n">
+        <v>5200</v>
+      </c>
+      <c r="U64" t="n">
+        <v>5300</v>
+      </c>
+      <c r="V64" t="n">
+        <v>7600</v>
+      </c>
+      <c r="W64" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X64" t="n">
+        <v>3600</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga Pakan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Pakan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -716,5020 +716,5020 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" t="n">
         <v>5251</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" t="n">
         <v>9590</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" t="n">
         <v>4410</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" t="n">
         <v>21809</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" t="n">
         <v>5090</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" t="n">
         <v>4684</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H2" t="n">
         <v>15920</v>
       </c>
-      <c r="I2" s="9" t="n">
+      <c r="I2" t="n">
         <v>6387</v>
       </c>
-      <c r="J2" s="9" t="n">
+      <c r="J2" t="n">
         <v>3950</v>
       </c>
-      <c r="K2" s="9" t="n">
+      <c r="K2" t="n">
         <v>7682</v>
       </c>
-      <c r="L2" s="9" t="n">
+      <c r="L2" t="n">
         <v>3002</v>
       </c>
-      <c r="M2" s="9" t="n">
+      <c r="M2" t="n">
         <v>5874</v>
       </c>
-      <c r="N2" s="9" t="n">
+      <c r="N2" t="n">
         <v>3489</v>
       </c>
-      <c r="O2" s="9" t="n">
+      <c r="O2" t="n">
         <v>8337</v>
       </c>
-      <c r="P2" s="9" t="n">
+      <c r="P2" t="n">
         <v>2726</v>
       </c>
-      <c r="Q2" s="9" t="n">
+      <c r="Q2" t="n">
         <v>2584</v>
       </c>
-      <c r="R2" s="9" t="n">
+      <c r="R2" t="n">
         <v>7936</v>
       </c>
-      <c r="S2" s="9" t="n">
+      <c r="S2" t="n">
         <v>4005</v>
       </c>
-      <c r="T2" s="9" t="n">
+      <c r="T2" t="n">
         <v>4524</v>
       </c>
-      <c r="U2" s="9" t="n">
+      <c r="U2" t="n">
         <v>5191</v>
       </c>
-      <c r="V2" s="9" t="n">
+      <c r="V2" t="n">
         <v>6941</v>
       </c>
-      <c r="W2" s="9" t="n">
+      <c r="W2" t="n">
         <v>5533</v>
       </c>
-      <c r="X2" s="9" t="n">
+      <c r="X2" t="n">
         <v>3346</v>
       </c>
-      <c r="Y2" s="10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" t="n">
         <v>5103</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" t="n">
         <v>9989</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" t="n">
         <v>3928</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" t="n">
         <v>21074</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" t="n">
         <v>4894</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" t="n">
         <v>4445</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="H3" t="n">
         <v>16176</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" t="n">
         <v>6317</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="J3" t="n">
         <v>3782</v>
       </c>
-      <c r="K3" s="9" t="n">
+      <c r="K3" t="n">
         <v>7151</v>
       </c>
-      <c r="L3" s="9" t="n">
+      <c r="L3" t="n">
         <v>3427</v>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="M3" t="n">
         <v>5387</v>
       </c>
-      <c r="N3" s="9" t="n">
+      <c r="N3" t="n">
         <v>3610</v>
       </c>
-      <c r="O3" s="9" t="n">
+      <c r="O3" t="n">
         <v>8246</v>
       </c>
-      <c r="P3" s="9" t="n">
+      <c r="P3" t="n">
         <v>2768</v>
       </c>
-      <c r="Q3" s="9" t="n">
+      <c r="Q3" t="n">
         <v>2546</v>
       </c>
-      <c r="R3" s="9" t="n">
+      <c r="R3" t="n">
         <v>8604</v>
       </c>
-      <c r="S3" s="9" t="n">
+      <c r="S3" t="n">
         <v>3829</v>
       </c>
-      <c r="T3" s="9" t="n">
+      <c r="T3" t="n">
         <v>4876</v>
       </c>
-      <c r="U3" s="9" t="n">
+      <c r="U3" t="n">
         <v>5720</v>
       </c>
-      <c r="V3" s="9" t="n">
+      <c r="V3" t="n">
         <v>7514</v>
       </c>
-      <c r="W3" s="9" t="n">
+      <c r="W3" t="n">
         <v>5059</v>
       </c>
-      <c r="X3" s="9" t="n">
+      <c r="X3" t="n">
         <v>3448</v>
       </c>
-      <c r="Y3" s="10" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" t="n">
         <v>5268</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" t="n">
         <v>9353</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" t="n">
         <v>3940</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" t="n">
         <v>20376</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" t="n">
         <v>5140</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" t="n">
         <v>4440</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" t="n">
         <v>15455</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" t="n">
         <v>6633</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" t="n">
         <v>3922</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" t="n">
         <v>7768</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" t="n">
         <v>3133</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" t="n">
         <v>5505</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" t="n">
         <v>3489</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" t="n">
         <v>7840</v>
       </c>
-      <c r="P4" s="9" t="n">
+      <c r="P4" t="n">
         <v>2948</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" t="n">
         <v>2622</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" t="n">
         <v>7827</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" t="n">
         <v>4207</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" t="n">
         <v>5070</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" t="n">
         <v>5343</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" t="n">
         <v>7638</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" t="n">
         <v>5312</v>
       </c>
-      <c r="X4" s="9" t="n">
+      <c r="X4" t="n">
         <v>3447</v>
       </c>
-      <c r="Y4" s="10" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" t="n">
         <v>5021</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" t="n">
         <v>9772</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" t="n">
         <v>3993</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" t="n">
         <v>21234</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" t="n">
         <v>4996</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" t="n">
         <v>4309</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" t="n">
         <v>15574</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" t="n">
         <v>6601</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" t="n">
         <v>3683</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" t="n">
         <v>7917</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" t="n">
         <v>3393</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" t="n">
         <v>5828</v>
       </c>
-      <c r="N5" s="9" t="n">
+      <c r="N5" t="n">
         <v>3497</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="O5" t="n">
         <v>7995</v>
       </c>
-      <c r="P5" s="9" t="n">
+      <c r="P5" t="n">
         <v>2888</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" t="n">
         <v>2556</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" t="n">
         <v>8706</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" t="n">
         <v>3788</v>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="T5" t="n">
         <v>4582</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="U5" t="n">
         <v>5261</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" t="n">
         <v>7141</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" t="n">
         <v>5430</v>
       </c>
-      <c r="X5" s="9" t="n">
+      <c r="X5" t="n">
         <v>3720</v>
       </c>
-      <c r="Y5" s="10" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" t="n">
         <v>5283</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" t="n">
         <v>9204</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" t="n">
         <v>4410</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" t="n">
         <v>23575</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" t="n">
         <v>5129</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" t="n">
         <v>4857</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" t="n">
         <v>15847</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" t="n">
         <v>6735</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" t="n">
         <v>3677</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" t="n">
         <v>7332</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" t="n">
         <v>3354</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" t="n">
         <v>5486</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" t="n">
         <v>3725</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" t="n">
         <v>8639</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="P6" t="n">
         <v>2609</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" t="n">
         <v>2559</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" t="n">
         <v>8029</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" t="n">
         <v>4105</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" t="n">
         <v>4541</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" t="n">
         <v>5513</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" t="n">
         <v>7845</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" t="n">
         <v>5455</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" t="n">
         <v>3225</v>
       </c>
-      <c r="Y6" s="10" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" t="n">
         <v>4863</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" t="n">
         <v>10262</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" t="n">
         <v>3996</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" t="n">
         <v>22159</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" t="n">
         <v>4663</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" t="n">
         <v>4740</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" t="n">
         <v>14983</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" t="n">
         <v>6089</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" t="n">
         <v>3789</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="K7" t="n">
         <v>7946</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" t="n">
         <v>2949</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" t="n">
         <v>5463</v>
       </c>
-      <c r="N7" s="9" t="n">
+      <c r="N7" t="n">
         <v>3546</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="O7" t="n">
         <v>8569</v>
       </c>
-      <c r="P7" s="9" t="n">
+      <c r="P7" t="n">
         <v>2647</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" t="n">
         <v>2667</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" t="n">
         <v>8539</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" t="n">
         <v>4270</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="T7" t="n">
         <v>4528</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" t="n">
         <v>5188</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" t="n">
         <v>7860</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" t="n">
         <v>5349</v>
       </c>
-      <c r="X7" s="9" t="n">
+      <c r="X7" t="n">
         <v>3730</v>
       </c>
-      <c r="Y7" s="10" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" t="n">
         <v>4785</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" t="n">
         <v>9656</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" t="n">
         <v>4494</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" t="n">
         <v>22694</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" t="n">
         <v>4716</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" t="n">
         <v>4756</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" t="n">
         <v>14611</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" t="n">
         <v>6172</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" t="n">
         <v>3706</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" t="n">
         <v>7328</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" t="n">
         <v>3183</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" t="n">
         <v>5427</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="N8" t="n">
         <v>3518</v>
       </c>
-      <c r="O8" s="9" t="n">
+      <c r="O8" t="n">
         <v>7768</v>
       </c>
-      <c r="P8" s="9" t="n">
+      <c r="P8" t="n">
         <v>2620</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" t="n">
         <v>2675</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" t="n">
         <v>8170</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" t="n">
         <v>4009</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="T8" t="n">
         <v>5109</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" t="n">
         <v>5332</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" t="n">
         <v>7815</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" t="n">
         <v>5225</v>
       </c>
-      <c r="X8" s="9" t="n">
+      <c r="X8" t="n">
         <v>3772</v>
       </c>
-      <c r="Y8" s="10" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" t="n">
         <v>5498</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" t="n">
         <v>9025</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" t="n">
         <v>3988</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" t="n">
         <v>23486</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" t="n">
         <v>4488</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" t="n">
         <v>4200</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" t="n">
         <v>14670</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" t="n">
         <v>6627</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" t="n">
         <v>4027</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" t="n">
         <v>7462</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" t="n">
         <v>3126</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" t="n">
         <v>6073</v>
       </c>
-      <c r="N9" s="9" t="n">
+      <c r="N9" t="n">
         <v>3585</v>
       </c>
-      <c r="O9" s="9" t="n">
+      <c r="O9" t="n">
         <v>7730</v>
       </c>
-      <c r="P9" s="9" t="n">
+      <c r="P9" t="n">
         <v>2808</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" t="n">
         <v>2532</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" t="n">
         <v>8877</v>
       </c>
-      <c r="S9" s="9" t="n">
+      <c r="S9" t="n">
         <v>4183</v>
       </c>
-      <c r="T9" s="9" t="n">
+      <c r="T9" t="n">
         <v>4917</v>
       </c>
-      <c r="U9" s="9" t="n">
+      <c r="U9" t="n">
         <v>5487</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" t="n">
         <v>7536</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" t="n">
         <v>4986</v>
       </c>
-      <c r="X9" s="9" t="n">
+      <c r="X9" t="n">
         <v>3253</v>
       </c>
-      <c r="Y9" s="10" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" t="n">
         <v>5046</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" t="n">
         <v>9172</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" t="n">
         <v>4058</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" t="n">
         <v>20398</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" t="n">
         <v>4915</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" t="n">
         <v>4299</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" t="n">
         <v>15168</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" t="n">
         <v>6324</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" t="n">
         <v>4002</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K10" t="n">
         <v>7402</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" t="n">
         <v>3022</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" t="n">
         <v>5427</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" t="n">
         <v>3635</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" t="n">
         <v>7397</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="P10" t="n">
         <v>2591</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" t="n">
         <v>2637</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" t="n">
         <v>8665</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="S10" t="n">
         <v>4175</v>
       </c>
-      <c r="T10" s="9" t="n">
+      <c r="T10" t="n">
         <v>4938</v>
       </c>
-      <c r="U10" s="9" t="n">
+      <c r="U10" t="n">
         <v>5454</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" t="n">
         <v>7731</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" t="n">
         <v>5183</v>
       </c>
-      <c r="X10" s="9" t="n">
+      <c r="X10" t="n">
         <v>3477</v>
       </c>
-      <c r="Y10" s="10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" t="n">
         <v>5418</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" t="n">
         <v>9997</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" t="n">
         <v>4187</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" t="n">
         <v>20998</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" t="n">
         <v>4517</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" t="n">
         <v>4765</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" t="n">
         <v>16193</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" t="n">
         <v>6220</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" t="n">
         <v>4004</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" t="n">
         <v>8018</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" t="n">
         <v>3401</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" t="n">
         <v>5460</v>
       </c>
-      <c r="N11" s="9" t="n">
+      <c r="N11" t="n">
         <v>3758</v>
       </c>
-      <c r="O11" s="9" t="n">
+      <c r="O11" t="n">
         <v>8104</v>
       </c>
-      <c r="P11" s="9" t="n">
+      <c r="P11" t="n">
         <v>2771</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" t="n">
         <v>2501</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" t="n">
         <v>9049</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="S11" t="n">
         <v>4315</v>
       </c>
-      <c r="T11" s="9" t="n">
+      <c r="T11" t="n">
         <v>4762</v>
       </c>
-      <c r="U11" s="9" t="n">
+      <c r="U11" t="n">
         <v>5792</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" t="n">
         <v>7714</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" t="n">
         <v>4855</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="X11" t="n">
         <v>3227</v>
       </c>
-      <c r="Y11" s="10" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" t="n">
         <v>5038</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" t="n">
         <v>9776</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" t="n">
         <v>3986</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" t="n">
         <v>23670</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" t="n">
         <v>4619</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" t="n">
         <v>4161</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" t="n">
         <v>16011</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" t="n">
         <v>6393</v>
       </c>
-      <c r="J12" s="9" t="n">
+      <c r="J12" t="n">
         <v>3641</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" t="n">
         <v>7250</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" t="n">
         <v>3347</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" t="n">
         <v>6104</v>
       </c>
-      <c r="N12" s="9" t="n">
+      <c r="N12" t="n">
         <v>3327</v>
       </c>
-      <c r="O12" s="9" t="n">
+      <c r="O12" t="n">
         <v>8004</v>
       </c>
-      <c r="P12" s="9" t="n">
+      <c r="P12" t="n">
         <v>2909</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" t="n">
         <v>2693</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" t="n">
         <v>8404</v>
       </c>
-      <c r="S12" s="9" t="n">
+      <c r="S12" t="n">
         <v>3992</v>
       </c>
-      <c r="T12" s="9" t="n">
+      <c r="T12" t="n">
         <v>4445</v>
       </c>
-      <c r="U12" s="9" t="n">
+      <c r="U12" t="n">
         <v>5103</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" t="n">
         <v>7968</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" t="n">
         <v>4951</v>
       </c>
-      <c r="X12" s="9" t="n">
+      <c r="X12" t="n">
         <v>3749</v>
       </c>
-      <c r="Y12" s="10" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" t="n">
         <v>5385</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" t="n">
         <v>9758</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" t="n">
         <v>4243</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" t="n">
         <v>23338</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" t="n">
         <v>5075</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" t="n">
         <v>4790</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" t="n">
         <v>15969</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" t="n">
         <v>6702</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" t="n">
         <v>3764</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" t="n">
         <v>8061</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" t="n">
         <v>3066</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" t="n">
         <v>6193</v>
       </c>
-      <c r="N13" s="9" t="n">
+      <c r="N13" t="n">
         <v>3691</v>
       </c>
-      <c r="O13" s="9" t="n">
+      <c r="O13" t="n">
         <v>8468</v>
       </c>
-      <c r="P13" s="9" t="n">
+      <c r="P13" t="n">
         <v>2886</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" t="n">
         <v>2421</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" t="n">
         <v>8190</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" t="n">
         <v>3911</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" t="n">
         <v>4864</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" t="n">
         <v>5301</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" t="n">
         <v>7043</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" t="n">
         <v>5475</v>
       </c>
-      <c r="X13" s="9" t="n">
+      <c r="X13" t="n">
         <v>3737</v>
       </c>
-      <c r="Y13" s="10" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" t="n">
         <v>5577</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" t="n">
         <v>9517</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" t="n">
         <v>3901</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" t="n">
         <v>22772</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" t="n">
         <v>4700</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" t="n">
         <v>4322</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="H14" t="n">
         <v>14171</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" t="n">
         <v>6658</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" t="n">
         <v>3575</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" t="n">
         <v>8020</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" t="n">
         <v>3252</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" t="n">
         <v>5968</v>
       </c>
-      <c r="N14" s="9" t="n">
+      <c r="N14" t="n">
         <v>3748</v>
       </c>
-      <c r="O14" s="9" t="n">
+      <c r="O14" t="n">
         <v>7893</v>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" t="n">
         <v>2596</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" t="n">
         <v>2605</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" t="n">
         <v>8716</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" t="n">
         <v>4295</v>
       </c>
-      <c r="T14" s="9" t="n">
+      <c r="T14" t="n">
         <v>4451</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" t="n">
         <v>5938</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" t="n">
         <v>7837</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" t="n">
         <v>5334</v>
       </c>
-      <c r="X14" s="9" t="n">
+      <c r="X14" t="n">
         <v>3252</v>
       </c>
-      <c r="Y14" s="10" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" t="n">
         <v>4860</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" t="n">
         <v>9511</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" t="n">
         <v>3942</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" t="n">
         <v>22962</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" t="n">
         <v>4789</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" t="n">
         <v>4238</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" t="n">
         <v>14246</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" t="n">
         <v>6475</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" t="n">
         <v>3825</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" t="n">
         <v>7318</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" t="n">
         <v>3039</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" t="n">
         <v>6165</v>
       </c>
-      <c r="N15" s="9" t="n">
+      <c r="N15" t="n">
         <v>3278</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" t="n">
         <v>7901</v>
       </c>
-      <c r="P15" s="9" t="n">
+      <c r="P15" t="n">
         <v>2975</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" t="n">
         <v>2553</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" t="n">
         <v>8770</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" t="n">
         <v>4002</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" t="n">
         <v>4966</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" t="n">
         <v>5649</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" t="n">
         <v>7851</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" t="n">
         <v>5012</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" t="n">
         <v>3367</v>
       </c>
-      <c r="Y15" s="10" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" t="n">
         <v>5554</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" t="n">
         <v>10375</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" t="n">
         <v>3897</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" t="n">
         <v>23452</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" t="n">
         <v>5108</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" t="n">
         <v>4326</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="H16" t="n">
         <v>16011</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" t="n">
         <v>6325</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" t="n">
         <v>3540</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" t="n">
         <v>7304</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" t="n">
         <v>3125</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" t="n">
         <v>5920</v>
       </c>
-      <c r="N16" s="9" t="n">
+      <c r="N16" t="n">
         <v>3399</v>
       </c>
-      <c r="O16" s="9" t="n">
+      <c r="O16" t="n">
         <v>7845</v>
       </c>
-      <c r="P16" s="9" t="n">
+      <c r="P16" t="n">
         <v>2749</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" t="n">
         <v>2485</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" t="n">
         <v>9096</v>
       </c>
-      <c r="S16" s="9" t="n">
+      <c r="S16" t="n">
         <v>4295</v>
       </c>
-      <c r="T16" s="9" t="n">
+      <c r="T16" t="n">
         <v>5089</v>
       </c>
-      <c r="U16" s="9" t="n">
+      <c r="U16" t="n">
         <v>5847</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" t="n">
         <v>7285</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" t="n">
         <v>5509</v>
       </c>
-      <c r="X16" s="9" t="n">
+      <c r="X16" t="n">
         <v>3731</v>
       </c>
-      <c r="Y16" s="10" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" t="n">
         <v>5333</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" t="n">
         <v>9416</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" t="n">
         <v>4085</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" t="n">
         <v>21959</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" t="n">
         <v>4423</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" t="n">
         <v>4664</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H17" t="n">
         <v>14613</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" t="n">
         <v>6047</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" t="n">
         <v>3913</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K17" t="n">
         <v>7982</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L17" t="n">
         <v>3064</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" t="n">
         <v>5955</v>
       </c>
-      <c r="N17" s="9" t="n">
+      <c r="N17" t="n">
         <v>3330</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="O17" t="n">
         <v>8410</v>
       </c>
-      <c r="P17" s="9" t="n">
+      <c r="P17" t="n">
         <v>2610</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" t="n">
         <v>2345</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" t="n">
         <v>7829</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="S17" t="n">
         <v>3729</v>
       </c>
-      <c r="T17" s="9" t="n">
+      <c r="T17" t="n">
         <v>4768</v>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="U17" t="n">
         <v>5475</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" t="n">
         <v>6912</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" t="n">
         <v>5499</v>
       </c>
-      <c r="X17" s="9" t="n">
+      <c r="X17" t="n">
         <v>3391</v>
       </c>
-      <c r="Y17" s="10" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" t="n">
         <v>5147</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" t="n">
         <v>9563</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" t="n">
         <v>4204</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" t="n">
         <v>21218</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" t="n">
         <v>5067</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" t="n">
         <v>4420</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" t="n">
         <v>14388</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" t="n">
         <v>6523</v>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="J18" t="n">
         <v>3633</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" t="n">
         <v>7776</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" t="n">
         <v>3398</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" t="n">
         <v>5929</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="N18" t="n">
         <v>3424</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" t="n">
         <v>8631</v>
       </c>
-      <c r="P18" s="9" t="n">
+      <c r="P18" t="n">
         <v>2805</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" t="n">
         <v>2678</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" t="n">
         <v>8136</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" t="n">
         <v>4055</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" t="n">
         <v>5070</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" t="n">
         <v>5060</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" t="n">
         <v>7101</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" t="n">
         <v>5339</v>
       </c>
-      <c r="X18" s="9" t="n">
+      <c r="X18" t="n">
         <v>3279</v>
       </c>
-      <c r="Y18" s="10" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" t="n">
         <v>4823</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" t="n">
         <v>9610</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" t="n">
         <v>4220</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" t="n">
         <v>22131</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" t="n">
         <v>4517</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" t="n">
         <v>4223</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" t="n">
         <v>15903</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" t="n">
         <v>6247</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" t="n">
         <v>3929</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" t="n">
         <v>7716</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" t="n">
         <v>2978</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" t="n">
         <v>6123</v>
       </c>
-      <c r="N19" s="9" t="n">
+      <c r="N19" t="n">
         <v>3244</v>
       </c>
-      <c r="O19" s="9" t="n">
+      <c r="O19" t="n">
         <v>8176</v>
       </c>
-      <c r="P19" s="9" t="n">
+      <c r="P19" t="n">
         <v>2877</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" t="n">
         <v>2685</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" t="n">
         <v>8904</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" t="n">
         <v>3681</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" t="n">
         <v>4718</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" t="n">
         <v>5065</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" t="n">
         <v>7527</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" t="n">
         <v>4812</v>
       </c>
-      <c r="X19" s="9" t="n">
+      <c r="X19" t="n">
         <v>3239</v>
       </c>
-      <c r="Y19" s="10" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" t="n">
         <v>4793</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" t="n">
         <v>9195</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" t="n">
         <v>4278</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" t="n">
         <v>22612</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" t="n">
         <v>4613</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" t="n">
         <v>4827</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" t="n">
         <v>14511</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" t="n">
         <v>6769</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="J20" t="n">
         <v>3643</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" t="n">
         <v>7125</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" t="n">
         <v>3004</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" t="n">
         <v>5981</v>
       </c>
-      <c r="N20" s="9" t="n">
+      <c r="N20" t="n">
         <v>3516</v>
       </c>
-      <c r="O20" s="9" t="n">
+      <c r="O20" t="n">
         <v>7839</v>
       </c>
-      <c r="P20" s="9" t="n">
+      <c r="P20" t="n">
         <v>2730</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" t="n">
         <v>2610</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" t="n">
         <v>8874</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="S20" t="n">
         <v>4284</v>
       </c>
-      <c r="T20" s="9" t="n">
+      <c r="T20" t="n">
         <v>4450</v>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" t="n">
         <v>5218</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" t="n">
         <v>7489</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" t="n">
         <v>4867</v>
       </c>
-      <c r="X20" s="9" t="n">
+      <c r="X20" t="n">
         <v>3738</v>
       </c>
-      <c r="Y20" s="10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" t="n">
         <v>4946</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" t="n">
         <v>10522</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" t="n">
         <v>4215</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" t="n">
         <v>21113</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" t="n">
         <v>4705</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" t="n">
         <v>4792</v>
       </c>
-      <c r="H21" s="9" t="n">
+      <c r="H21" t="n">
         <v>15924</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" t="n">
         <v>6224</v>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="J21" t="n">
         <v>4093</v>
       </c>
-      <c r="K21" s="9" t="n">
+      <c r="K21" t="n">
         <v>7089</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" t="n">
         <v>3074</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" t="n">
         <v>5787</v>
       </c>
-      <c r="N21" s="9" t="n">
+      <c r="N21" t="n">
         <v>3778</v>
       </c>
-      <c r="O21" s="9" t="n">
+      <c r="O21" t="n">
         <v>8023</v>
       </c>
-      <c r="P21" s="9" t="n">
+      <c r="P21" t="n">
         <v>2625</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" t="n">
         <v>2483</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" t="n">
         <v>7834</v>
       </c>
-      <c r="S21" s="9" t="n">
+      <c r="S21" t="n">
         <v>3846</v>
       </c>
-      <c r="T21" s="9" t="n">
+      <c r="T21" t="n">
         <v>4619</v>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="U21" t="n">
         <v>5811</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" t="n">
         <v>8041</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" t="n">
         <v>4969</v>
       </c>
-      <c r="X21" s="9" t="n">
+      <c r="X21" t="n">
         <v>3640</v>
       </c>
-      <c r="Y21" s="10" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" t="n">
         <v>5334</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" t="n">
         <v>9040</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" t="n">
         <v>4223</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" t="n">
         <v>22607</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" t="n">
         <v>5028</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" t="n">
         <v>4576</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" t="n">
         <v>15321</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" t="n">
         <v>6910</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J22" t="n">
         <v>3880</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" t="n">
         <v>7239</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" t="n">
         <v>3373</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" t="n">
         <v>5393</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" t="n">
         <v>3333</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" t="n">
         <v>7430</v>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="P22" t="n">
         <v>2914</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" t="n">
         <v>2641</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" t="n">
         <v>8698</v>
       </c>
-      <c r="S22" s="9" t="n">
+      <c r="S22" t="n">
         <v>3845</v>
       </c>
-      <c r="T22" s="9" t="n">
+      <c r="T22" t="n">
         <v>4448</v>
       </c>
-      <c r="U22" s="9" t="n">
+      <c r="U22" t="n">
         <v>5455</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" t="n">
         <v>7831</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" t="n">
         <v>5085</v>
       </c>
-      <c r="X22" s="9" t="n">
+      <c r="X22" t="n">
         <v>3346</v>
       </c>
-      <c r="Y22" s="10" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" t="n">
         <v>4990</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" t="n">
         <v>10478</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" t="n">
         <v>4196</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" t="n">
         <v>23508</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" t="n">
         <v>4799</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" t="n">
         <v>4353</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="H23" t="n">
         <v>16159</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" t="n">
         <v>6078</v>
       </c>
-      <c r="J23" s="9" t="n">
+      <c r="J23" t="n">
         <v>3643</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" t="n">
         <v>7447</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" t="n">
         <v>3421</v>
       </c>
-      <c r="M23" s="9" t="n">
+      <c r="M23" t="n">
         <v>5396</v>
       </c>
-      <c r="N23" s="9" t="n">
+      <c r="N23" t="n">
         <v>3235</v>
       </c>
-      <c r="O23" s="9" t="n">
+      <c r="O23" t="n">
         <v>8235</v>
       </c>
-      <c r="P23" s="9" t="n">
+      <c r="P23" t="n">
         <v>2779</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" t="n">
         <v>2344</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" t="n">
         <v>8397</v>
       </c>
-      <c r="S23" s="9" t="n">
+      <c r="S23" t="n">
         <v>3841</v>
       </c>
-      <c r="T23" s="9" t="n">
+      <c r="T23" t="n">
         <v>4682</v>
       </c>
-      <c r="U23" s="9" t="n">
+      <c r="U23" t="n">
         <v>5250</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" t="n">
         <v>8061</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" t="n">
         <v>5052</v>
       </c>
-      <c r="X23" s="9" t="n">
+      <c r="X23" t="n">
         <v>3417</v>
       </c>
-      <c r="Y23" s="10" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" t="n">
         <v>5429</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" t="n">
         <v>9335</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" t="n">
         <v>4164</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" t="n">
         <v>22506</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" t="n">
         <v>4577</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" t="n">
         <v>4390</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" t="n">
         <v>14025</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" t="n">
         <v>6865</v>
       </c>
-      <c r="J24" s="9" t="n">
+      <c r="J24" t="n">
         <v>4043</v>
       </c>
-      <c r="K24" s="9" t="n">
+      <c r="K24" t="n">
         <v>7518</v>
       </c>
-      <c r="L24" s="9" t="n">
+      <c r="L24" t="n">
         <v>2981</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" t="n">
         <v>6047</v>
       </c>
-      <c r="N24" s="9" t="n">
+      <c r="N24" t="n">
         <v>3633</v>
       </c>
-      <c r="O24" s="9" t="n">
+      <c r="O24" t="n">
         <v>7668</v>
       </c>
-      <c r="P24" s="9" t="n">
+      <c r="P24" t="n">
         <v>3012</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" t="n">
         <v>2633</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" t="n">
         <v>8590</v>
       </c>
-      <c r="S24" s="9" t="n">
+      <c r="S24" t="n">
         <v>3816</v>
       </c>
-      <c r="T24" s="9" t="n">
+      <c r="T24" t="n">
         <v>4519</v>
       </c>
-      <c r="U24" s="9" t="n">
+      <c r="U24" t="n">
         <v>5529</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" t="n">
         <v>7529</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" t="n">
         <v>5503</v>
       </c>
-      <c r="X24" s="9" t="n">
+      <c r="X24" t="n">
         <v>3347</v>
       </c>
-      <c r="Y24" s="10" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" t="n">
         <v>5263</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" t="n">
         <v>10508</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" t="n">
         <v>4282</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" t="n">
         <v>20922</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" t="n">
         <v>4551</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" t="n">
         <v>4246</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" t="n">
         <v>14414</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" t="n">
         <v>6837</v>
       </c>
-      <c r="J25" s="9" t="n">
+      <c r="J25" t="n">
         <v>4091</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" t="n">
         <v>7194</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" t="n">
         <v>3017</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" t="n">
         <v>5900</v>
       </c>
-      <c r="N25" s="9" t="n">
+      <c r="N25" t="n">
         <v>3426</v>
       </c>
-      <c r="O25" s="9" t="n">
+      <c r="O25" t="n">
         <v>7640</v>
       </c>
-      <c r="P25" s="9" t="n">
+      <c r="P25" t="n">
         <v>2842</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" t="n">
         <v>2336</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" t="n">
         <v>8259</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" t="n">
         <v>3780</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" t="n">
         <v>4643</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" t="n">
         <v>5251</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" t="n">
         <v>7718</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" t="n">
         <v>5320</v>
       </c>
-      <c r="X25" s="9" t="n">
+      <c r="X25" t="n">
         <v>3346</v>
       </c>
-      <c r="Y25" s="10" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" t="n">
         <v>5016</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" t="n">
         <v>9928</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" t="n">
         <v>4048</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" t="n">
         <v>22572</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" t="n">
         <v>4459</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" t="n">
         <v>4722</v>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="H26" t="n">
         <v>14029</v>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="I26" t="n">
         <v>6052</v>
       </c>
-      <c r="J26" s="9" t="n">
+      <c r="J26" t="n">
         <v>3745</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" t="n">
         <v>6971</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" t="n">
         <v>3241</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" t="n">
         <v>5522</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="N26" t="n">
         <v>3323</v>
       </c>
-      <c r="O26" s="9" t="n">
+      <c r="O26" t="n">
         <v>7860</v>
       </c>
-      <c r="P26" s="9" t="n">
+      <c r="P26" t="n">
         <v>3000</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" t="n">
         <v>2698</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" t="n">
         <v>8639</v>
       </c>
-      <c r="S26" s="9" t="n">
+      <c r="S26" t="n">
         <v>4055</v>
       </c>
-      <c r="T26" s="9" t="n">
+      <c r="T26" t="n">
         <v>4504</v>
       </c>
-      <c r="U26" s="9" t="n">
+      <c r="U26" t="n">
         <v>5664</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" t="n">
         <v>6968</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" t="n">
         <v>5190</v>
       </c>
-      <c r="X26" s="9" t="n">
+      <c r="X26" t="n">
         <v>3765</v>
       </c>
-      <c r="Y26" s="10" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" t="n">
         <v>5012</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" t="n">
         <v>9740</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" t="n">
         <v>4059</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" t="n">
         <v>20980</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" t="n">
         <v>4858</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" t="n">
         <v>4632</v>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="H27" t="n">
         <v>15456</v>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I27" t="n">
         <v>6022</v>
       </c>
-      <c r="J27" s="9" t="n">
+      <c r="J27" t="n">
         <v>3696</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" t="n">
         <v>7368</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" t="n">
         <v>3172</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" t="n">
         <v>5650</v>
       </c>
-      <c r="N27" s="9" t="n">
+      <c r="N27" t="n">
         <v>3651</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" t="n">
         <v>7558</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" t="n">
         <v>2815</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" t="n">
         <v>2639</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" t="n">
         <v>8048</v>
       </c>
-      <c r="S27" s="9" t="n">
+      <c r="S27" t="n">
         <v>3898</v>
       </c>
-      <c r="T27" s="9" t="n">
+      <c r="T27" t="n">
         <v>4866</v>
       </c>
-      <c r="U27" s="9" t="n">
+      <c r="U27" t="n">
         <v>5380</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" t="n">
         <v>7490</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" t="n">
         <v>4859</v>
       </c>
-      <c r="X27" s="9" t="n">
+      <c r="X27" t="n">
         <v>3301</v>
       </c>
-      <c r="Y27" s="10" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" t="n">
         <v>4986</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" t="n">
         <v>9792</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" t="n">
         <v>4046</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" t="n">
         <v>20887</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" t="n">
         <v>4489</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" t="n">
         <v>4834</v>
       </c>
-      <c r="H28" s="9" t="n">
+      <c r="H28" t="n">
         <v>14920</v>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="I28" t="n">
         <v>6890</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" t="n">
         <v>4041</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" t="n">
         <v>7072</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" t="n">
         <v>3380</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" t="n">
         <v>5695</v>
       </c>
-      <c r="N28" s="9" t="n">
+      <c r="N28" t="n">
         <v>3316</v>
       </c>
-      <c r="O28" s="9" t="n">
+      <c r="O28" t="n">
         <v>7720</v>
       </c>
-      <c r="P28" s="9" t="n">
+      <c r="P28" t="n">
         <v>2751</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" t="n">
         <v>2610</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" t="n">
         <v>8651</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S28" t="n">
         <v>3853</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T28" t="n">
         <v>4869</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" t="n">
         <v>5239</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" t="n">
         <v>8040</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" t="n">
         <v>4965</v>
       </c>
-      <c r="X28" s="9" t="n">
+      <c r="X28" t="n">
         <v>3312</v>
       </c>
-      <c r="Y28" s="10" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B29" t="n">
         <v>5426</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" t="n">
         <v>10374</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" t="n">
         <v>4038</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" t="n">
         <v>22282</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" t="n">
         <v>5052</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" t="n">
         <v>4288</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" t="n">
         <v>14943</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I29" t="n">
         <v>6821</v>
       </c>
-      <c r="J29" s="9" t="n">
+      <c r="J29" t="n">
         <v>4046</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" t="n">
         <v>6966</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" t="n">
         <v>2980</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" t="n">
         <v>5382</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" t="n">
         <v>3270</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" t="n">
         <v>7653</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" t="n">
         <v>2675</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" t="n">
         <v>2455</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" t="n">
         <v>8131</v>
       </c>
-      <c r="S29" s="9" t="n">
+      <c r="S29" t="n">
         <v>3871</v>
       </c>
-      <c r="T29" s="9" t="n">
+      <c r="T29" t="n">
         <v>4544</v>
       </c>
-      <c r="U29" s="9" t="n">
+      <c r="U29" t="n">
         <v>5421</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" t="n">
         <v>8031</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" t="n">
         <v>5405</v>
       </c>
-      <c r="X29" s="9" t="n">
+      <c r="X29" t="n">
         <v>3461</v>
       </c>
-      <c r="Y29" s="10" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" t="n">
         <v>4897</v>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" t="n">
         <v>9850</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" t="n">
         <v>4200</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" t="n">
         <v>20298</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" t="n">
         <v>4617</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" t="n">
         <v>4711</v>
       </c>
-      <c r="H30" s="9" t="n">
+      <c r="H30" t="n">
         <v>15619</v>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="I30" t="n">
         <v>7010</v>
       </c>
-      <c r="J30" s="9" t="n">
+      <c r="J30" t="n">
         <v>3598</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" t="n">
         <v>7883</v>
       </c>
-      <c r="L30" s="9" t="n">
+      <c r="L30" t="n">
         <v>3348</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" t="n">
         <v>6082</v>
       </c>
-      <c r="N30" s="9" t="n">
+      <c r="N30" t="n">
         <v>3475</v>
       </c>
-      <c r="O30" s="9" t="n">
+      <c r="O30" t="n">
         <v>8010</v>
       </c>
-      <c r="P30" s="9" t="n">
+      <c r="P30" t="n">
         <v>2582</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" t="n">
         <v>2676</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" t="n">
         <v>8486</v>
       </c>
-      <c r="S30" s="9" t="n">
+      <c r="S30" t="n">
         <v>3797</v>
       </c>
-      <c r="T30" s="9" t="n">
+      <c r="T30" t="n">
         <v>5006</v>
       </c>
-      <c r="U30" s="9" t="n">
+      <c r="U30" t="n">
         <v>5546</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" t="n">
         <v>7708</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" t="n">
         <v>5444</v>
       </c>
-      <c r="X30" s="9" t="n">
+      <c r="X30" t="n">
         <v>3516</v>
       </c>
-      <c r="Y30" s="10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
+      <c r="B31" t="n">
         <v>5613</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" t="n">
         <v>10176</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" t="n">
         <v>4013</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" t="n">
         <v>22322</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" t="n">
         <v>4795</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" t="n">
         <v>4172</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" t="n">
         <v>15822</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" t="n">
         <v>6484</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" t="n">
         <v>3550</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" t="n">
         <v>7664</v>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L31" t="n">
         <v>3448</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" t="n">
         <v>6062</v>
       </c>
-      <c r="N31" s="9" t="n">
+      <c r="N31" t="n">
         <v>3599</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" t="n">
         <v>8431</v>
       </c>
-      <c r="P31" s="9" t="n">
+      <c r="P31" t="n">
         <v>2604</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" t="n">
         <v>2622</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" t="n">
         <v>7982</v>
       </c>
-      <c r="S31" s="9" t="n">
+      <c r="S31" t="n">
         <v>3898</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" t="n">
         <v>4707</v>
       </c>
-      <c r="U31" s="9" t="n">
+      <c r="U31" t="n">
         <v>5794</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" t="n">
         <v>7654</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" t="n">
         <v>5217</v>
       </c>
-      <c r="X31" s="9" t="n">
+      <c r="X31" t="n">
         <v>3701</v>
       </c>
-      <c r="Y31" s="10" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" t="n">
         <v>4875</v>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" t="n">
         <v>10457</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" t="n">
         <v>4404</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" t="n">
         <v>20426</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" t="n">
         <v>4466</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" t="n">
         <v>4466</v>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H32" t="n">
         <v>14279</v>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="I32" t="n">
         <v>6927</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" t="n">
         <v>3723</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" t="n">
         <v>7703</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" t="n">
         <v>3243</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" t="n">
         <v>5475</v>
       </c>
-      <c r="N32" s="9" t="n">
+      <c r="N32" t="n">
         <v>3574</v>
       </c>
-      <c r="O32" s="9" t="n">
+      <c r="O32" t="n">
         <v>8178</v>
       </c>
-      <c r="P32" s="9" t="n">
+      <c r="P32" t="n">
         <v>2999</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" t="n">
         <v>2457</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" t="n">
         <v>8254</v>
       </c>
-      <c r="S32" s="9" t="n">
+      <c r="S32" t="n">
         <v>3886</v>
       </c>
-      <c r="T32" s="9" t="n">
+      <c r="T32" t="n">
         <v>4660</v>
       </c>
-      <c r="U32" s="9" t="n">
+      <c r="U32" t="n">
         <v>5220</v>
       </c>
-      <c r="V32" s="9" t="n">
+      <c r="V32" t="n">
         <v>6936</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" t="n">
         <v>5460</v>
       </c>
-      <c r="X32" s="9" t="n">
+      <c r="X32" t="n">
         <v>3361</v>
       </c>
-      <c r="Y32" s="10" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
+      <c r="B33" t="n">
         <v>5310</v>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" t="n">
         <v>10333</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" t="n">
         <v>4074</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" t="n">
         <v>21564</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" t="n">
         <v>4939</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" t="n">
         <v>4150</v>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" t="n">
         <v>14687</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" t="n">
         <v>6801</v>
       </c>
-      <c r="J33" s="9" t="n">
+      <c r="J33" t="n">
         <v>4034</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" t="n">
         <v>7415</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" t="n">
         <v>3298</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" t="n">
         <v>5739</v>
       </c>
-      <c r="N33" s="9" t="n">
+      <c r="N33" t="n">
         <v>3548</v>
       </c>
-      <c r="O33" s="9" t="n">
+      <c r="O33" t="n">
         <v>7955</v>
       </c>
-      <c r="P33" s="9" t="n">
+      <c r="P33" t="n">
         <v>2742</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" t="n">
         <v>2664</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" t="n">
         <v>8289</v>
       </c>
-      <c r="S33" s="9" t="n">
+      <c r="S33" t="n">
         <v>3985</v>
       </c>
-      <c r="T33" s="9" t="n">
+      <c r="T33" t="n">
         <v>4670</v>
       </c>
-      <c r="U33" s="9" t="n">
+      <c r="U33" t="n">
         <v>5829</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" t="n">
         <v>7111</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" t="n">
         <v>5320</v>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="X33" t="n">
         <v>3464</v>
       </c>
-      <c r="Y33" s="10" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" t="n">
         <v>4902</v>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" t="n">
         <v>10218</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" t="n">
         <v>4067</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" t="n">
         <v>21792</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" t="n">
         <v>4838</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" t="n">
         <v>4844</v>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="H34" t="n">
         <v>15549</v>
       </c>
-      <c r="I34" s="9" t="n">
+      <c r="I34" t="n">
         <v>6838</v>
       </c>
-      <c r="J34" s="9" t="n">
+      <c r="J34" t="n">
         <v>3512</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" t="n">
         <v>7429</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" t="n">
         <v>2990</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" t="n">
         <v>5549</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="N34" t="n">
         <v>3422</v>
       </c>
-      <c r="O34" s="9" t="n">
+      <c r="O34" t="n">
         <v>7470</v>
       </c>
-      <c r="P34" s="9" t="n">
+      <c r="P34" t="n">
         <v>2609</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" t="n">
         <v>2595</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" t="n">
         <v>8370</v>
       </c>
-      <c r="S34" s="9" t="n">
+      <c r="S34" t="n">
         <v>3844</v>
       </c>
-      <c r="T34" s="9" t="n">
+      <c r="T34" t="n">
         <v>4504</v>
       </c>
-      <c r="U34" s="9" t="n">
+      <c r="U34" t="n">
         <v>5660</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" t="n">
         <v>8063</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" t="n">
         <v>5437</v>
       </c>
-      <c r="X34" s="9" t="n">
+      <c r="X34" t="n">
         <v>3458</v>
       </c>
-      <c r="Y34" s="10" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
+      <c r="B35" t="n">
         <v>5607</v>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" t="n">
         <v>9333</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" t="n">
         <v>4234</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" t="n">
         <v>22836</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" t="n">
         <v>5176</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" t="n">
         <v>4248</v>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="H35" t="n">
         <v>15392</v>
       </c>
-      <c r="I35" s="9" t="n">
+      <c r="I35" t="n">
         <v>6333</v>
       </c>
-      <c r="J35" s="9" t="n">
+      <c r="J35" t="n">
         <v>3659</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" t="n">
         <v>7498</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" t="n">
         <v>3209</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" t="n">
         <v>5520</v>
       </c>
-      <c r="N35" s="9" t="n">
+      <c r="N35" t="n">
         <v>3454</v>
       </c>
-      <c r="O35" s="9" t="n">
+      <c r="O35" t="n">
         <v>7638</v>
       </c>
-      <c r="P35" s="9" t="n">
+      <c r="P35" t="n">
         <v>2710</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" t="n">
         <v>2602</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" t="n">
         <v>8450</v>
       </c>
-      <c r="S35" s="9" t="n">
+      <c r="S35" t="n">
         <v>4299</v>
       </c>
-      <c r="T35" s="9" t="n">
+      <c r="T35" t="n">
         <v>4621</v>
       </c>
-      <c r="U35" s="9" t="n">
+      <c r="U35" t="n">
         <v>5466</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" t="n">
         <v>7931</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" t="n">
         <v>4945</v>
       </c>
-      <c r="X35" s="9" t="n">
+      <c r="X35" t="n">
         <v>3272</v>
       </c>
-      <c r="Y35" s="10" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" t="n">
         <v>4790</v>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" t="n">
         <v>10406</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" t="n">
         <v>4476</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" t="n">
         <v>21404</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" t="n">
         <v>4999</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" t="n">
         <v>4459</v>
       </c>
-      <c r="H36" s="9" t="n">
+      <c r="H36" t="n">
         <v>14261</v>
       </c>
-      <c r="I36" s="9" t="n">
+      <c r="I36" t="n">
         <v>7012</v>
       </c>
-      <c r="J36" s="9" t="n">
+      <c r="J36" t="n">
         <v>3546</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" t="n">
         <v>7097</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" t="n">
         <v>3107</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" t="n">
         <v>5640</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="N36" t="n">
         <v>3666</v>
       </c>
-      <c r="O36" s="9" t="n">
+      <c r="O36" t="n">
         <v>8189</v>
       </c>
-      <c r="P36" s="9" t="n">
+      <c r="P36" t="n">
         <v>2710</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" t="n">
         <v>2342</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" t="n">
         <v>9137</v>
       </c>
-      <c r="S36" s="9" t="n">
+      <c r="S36" t="n">
         <v>3998</v>
       </c>
-      <c r="T36" s="9" t="n">
+      <c r="T36" t="n">
         <v>4468</v>
       </c>
-      <c r="U36" s="9" t="n">
+      <c r="U36" t="n">
         <v>5318</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" t="n">
         <v>7838</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" t="n">
         <v>4988</v>
       </c>
-      <c r="X36" s="9" t="n">
+      <c r="X36" t="n">
         <v>3240</v>
       </c>
-      <c r="Y36" s="10" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
+      <c r="B37" t="n">
         <v>5253</v>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" t="n">
         <v>10310</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" t="n">
         <v>4328</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" t="n">
         <v>23360</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" t="n">
         <v>5106</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G37" t="n">
         <v>4331</v>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="H37" t="n">
         <v>14292</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I37" t="n">
         <v>6269</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="J37" t="n">
         <v>3759</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" t="n">
         <v>8063</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" t="n">
         <v>3384</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" t="n">
         <v>6090</v>
       </c>
-      <c r="N37" s="9" t="n">
+      <c r="N37" t="n">
         <v>3344</v>
       </c>
-      <c r="O37" s="9" t="n">
+      <c r="O37" t="n">
         <v>7751</v>
       </c>
-      <c r="P37" s="9" t="n">
+      <c r="P37" t="n">
         <v>2663</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="Q37" t="n">
         <v>2363</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" t="n">
         <v>7905</v>
       </c>
-      <c r="S37" s="9" t="n">
+      <c r="S37" t="n">
         <v>4086</v>
       </c>
-      <c r="T37" s="9" t="n">
+      <c r="T37" t="n">
         <v>4520</v>
       </c>
-      <c r="U37" s="9" t="n">
+      <c r="U37" t="n">
         <v>5178</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" t="n">
         <v>7869</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" t="n">
         <v>4993</v>
       </c>
-      <c r="X37" s="9" t="n">
+      <c r="X37" t="n">
         <v>3342</v>
       </c>
-      <c r="Y37" s="10" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" t="n">
         <v>5412</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" t="n">
         <v>9530</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" t="n">
         <v>4142</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" t="n">
         <v>21604</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" t="n">
         <v>5002</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" t="n">
         <v>4185</v>
       </c>
-      <c r="H38" s="9" t="n">
+      <c r="H38" t="n">
         <v>13902</v>
       </c>
-      <c r="I38" s="9" t="n">
+      <c r="I38" t="n">
         <v>6662</v>
       </c>
-      <c r="J38" s="9" t="n">
+      <c r="J38" t="n">
         <v>3631</v>
       </c>
-      <c r="K38" s="9" t="n">
+      <c r="K38" t="n">
         <v>7642</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" t="n">
         <v>3125</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" t="n">
         <v>6248</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="N38" t="n">
         <v>3573</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="O38" t="n">
         <v>7768</v>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="P38" t="n">
         <v>2639</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" t="n">
         <v>2606</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" t="n">
         <v>9083</v>
       </c>
-      <c r="S38" s="9" t="n">
+      <c r="S38" t="n">
         <v>4253</v>
       </c>
-      <c r="T38" s="9" t="n">
+      <c r="T38" t="n">
         <v>4937</v>
       </c>
-      <c r="U38" s="9" t="n">
+      <c r="U38" t="n">
         <v>5525</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" t="n">
         <v>7578</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" t="n">
         <v>5439</v>
       </c>
-      <c r="X38" s="9" t="n">
+      <c r="X38" t="n">
         <v>3489</v>
       </c>
-      <c r="Y38" s="10" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n">
+      <c r="B39" t="n">
         <v>4980</v>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" t="n">
         <v>9627</v>
       </c>
-      <c r="D39" s="9" t="n">
+      <c r="D39" t="n">
         <v>4040</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" t="n">
         <v>20698</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" t="n">
         <v>4943</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" t="n">
         <v>4426</v>
       </c>
-      <c r="H39" s="9" t="n">
+      <c r="H39" t="n">
         <v>15381</v>
       </c>
-      <c r="I39" s="9" t="n">
+      <c r="I39" t="n">
         <v>6714</v>
       </c>
-      <c r="J39" s="9" t="n">
+      <c r="J39" t="n">
         <v>3756</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" t="n">
         <v>7567</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" t="n">
         <v>3026</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" t="n">
         <v>5820</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="N39" t="n">
         <v>3536</v>
       </c>
-      <c r="O39" s="9" t="n">
+      <c r="O39" t="n">
         <v>7735</v>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="P39" t="n">
         <v>2798</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" t="n">
         <v>2540</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" t="n">
         <v>9015</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="S39" t="n">
         <v>3747</v>
       </c>
-      <c r="T39" s="9" t="n">
+      <c r="T39" t="n">
         <v>4795</v>
       </c>
-      <c r="U39" s="9" t="n">
+      <c r="U39" t="n">
         <v>5066</v>
       </c>
-      <c r="V39" s="9" t="n">
+      <c r="V39" t="n">
         <v>8089</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" t="n">
         <v>5125</v>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="X39" t="n">
         <v>3682</v>
       </c>
-      <c r="Y39" s="10" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" t="n">
         <v>5373</v>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" t="n">
         <v>10278</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" t="n">
         <v>4298</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" t="n">
         <v>23053</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" t="n">
         <v>4961</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" t="n">
         <v>4451</v>
       </c>
-      <c r="H40" s="9" t="n">
+      <c r="H40" t="n">
         <v>15695</v>
       </c>
-      <c r="I40" s="9" t="n">
+      <c r="I40" t="n">
         <v>6611</v>
       </c>
-      <c r="J40" s="9" t="n">
+      <c r="J40" t="n">
         <v>4025</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" t="n">
         <v>7875</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" t="n">
         <v>3316</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" t="n">
         <v>5636</v>
       </c>
-      <c r="N40" s="9" t="n">
+      <c r="N40" t="n">
         <v>3485</v>
       </c>
-      <c r="O40" s="9" t="n">
+      <c r="O40" t="n">
         <v>7897</v>
       </c>
-      <c r="P40" s="9" t="n">
+      <c r="P40" t="n">
         <v>2921</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" t="n">
         <v>2389</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" t="n">
         <v>8905</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="S40" t="n">
         <v>4073</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="T40" t="n">
         <v>4537</v>
       </c>
-      <c r="U40" s="9" t="n">
+      <c r="U40" t="n">
         <v>5389</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" t="n">
         <v>7040</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" t="n">
         <v>5602</v>
       </c>
-      <c r="X40" s="9" t="n">
+      <c r="X40" t="n">
         <v>3546</v>
       </c>
-      <c r="Y40" s="10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B41" t="n">
         <v>5556</v>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" t="n">
         <v>9147</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" t="n">
         <v>4490</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" t="n">
         <v>22617</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" t="n">
         <v>4744</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" t="n">
         <v>4153</v>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="H41" t="n">
         <v>15548</v>
       </c>
-      <c r="I41" s="9" t="n">
+      <c r="I41" t="n">
         <v>6330</v>
       </c>
-      <c r="J41" s="9" t="n">
+      <c r="J41" t="n">
         <v>3788</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" t="n">
         <v>7725</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" t="n">
         <v>3077</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" t="n">
         <v>5755</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" t="n">
         <v>3540</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" t="n">
         <v>8184</v>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="P41" t="n">
         <v>2863</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" t="n">
         <v>2648</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" t="n">
         <v>8318</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="S41" t="n">
         <v>3793</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" t="n">
         <v>4471</v>
       </c>
-      <c r="U41" s="9" t="n">
+      <c r="U41" t="n">
         <v>5787</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" t="n">
         <v>7239</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" t="n">
         <v>4905</v>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" t="n">
         <v>3474</v>
       </c>
-      <c r="Y41" s="10" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" t="n">
         <v>4871</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" t="n">
         <v>10104</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" t="n">
         <v>3950</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" t="n">
         <v>22872</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" t="n">
         <v>5048</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" t="n">
         <v>4501</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" t="n">
         <v>14580</v>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" t="n">
         <v>6287</v>
       </c>
-      <c r="J42" s="9" t="n">
+      <c r="J42" t="n">
         <v>3879</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" t="n">
         <v>7881</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" t="n">
         <v>3192</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" t="n">
         <v>5699</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" t="n">
         <v>3737</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" t="n">
         <v>7950</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" t="n">
         <v>2709</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" t="n">
         <v>2601</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" t="n">
         <v>8602</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" t="n">
         <v>4245</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" t="n">
         <v>4418</v>
       </c>
-      <c r="U42" s="9" t="n">
+      <c r="U42" t="n">
         <v>5461</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" t="n">
         <v>7871</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" t="n">
         <v>5144</v>
       </c>
-      <c r="X42" s="9" t="n">
+      <c r="X42" t="n">
         <v>3406</v>
       </c>
-      <c r="Y42" s="10" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
+      <c r="B43" t="n">
         <v>5058</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="C43" t="n">
         <v>9240</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" t="n">
         <v>4188</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" t="n">
         <v>23097</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" t="n">
         <v>4979</v>
       </c>
-      <c r="G43" s="9" t="n">
+      <c r="G43" t="n">
         <v>4419</v>
       </c>
-      <c r="H43" s="9" t="n">
+      <c r="H43" t="n">
         <v>15468</v>
       </c>
-      <c r="I43" s="9" t="n">
+      <c r="I43" t="n">
         <v>6418</v>
       </c>
-      <c r="J43" s="9" t="n">
+      <c r="J43" t="n">
         <v>3621</v>
       </c>
-      <c r="K43" s="9" t="n">
+      <c r="K43" t="n">
         <v>7615</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" t="n">
         <v>3107</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" t="n">
         <v>5386</v>
       </c>
-      <c r="N43" s="9" t="n">
+      <c r="N43" t="n">
         <v>3457</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="O43" t="n">
         <v>7559</v>
       </c>
-      <c r="P43" s="9" t="n">
+      <c r="P43" t="n">
         <v>2576</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" t="n">
         <v>2440</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" t="n">
         <v>8157</v>
       </c>
-      <c r="S43" s="9" t="n">
+      <c r="S43" t="n">
         <v>4121</v>
       </c>
-      <c r="T43" s="9" t="n">
+      <c r="T43" t="n">
         <v>5168</v>
       </c>
-      <c r="U43" s="9" t="n">
+      <c r="U43" t="n">
         <v>5483</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" t="n">
         <v>7609</v>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="W43" t="n">
         <v>5557</v>
       </c>
-      <c r="X43" s="9" t="n">
+      <c r="X43" t="n">
         <v>3754</v>
       </c>
-      <c r="Y43" s="10" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" t="n">
         <v>4956</v>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="C44" t="n">
         <v>9151</v>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="D44" t="n">
         <v>4345</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" t="n">
         <v>20570</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" t="n">
         <v>5155</v>
       </c>
-      <c r="G44" s="9" t="n">
+      <c r="G44" t="n">
         <v>4319</v>
       </c>
-      <c r="H44" s="9" t="n">
+      <c r="H44" t="n">
         <v>14603</v>
       </c>
-      <c r="I44" s="9" t="n">
+      <c r="I44" t="n">
         <v>6478</v>
       </c>
-      <c r="J44" s="9" t="n">
+      <c r="J44" t="n">
         <v>3735</v>
       </c>
-      <c r="K44" s="9" t="n">
+      <c r="K44" t="n">
         <v>8052</v>
       </c>
-      <c r="L44" s="9" t="n">
+      <c r="L44" t="n">
         <v>3050</v>
       </c>
-      <c r="M44" s="9" t="n">
+      <c r="M44" t="n">
         <v>5725</v>
       </c>
-      <c r="N44" s="9" t="n">
+      <c r="N44" t="n">
         <v>3593</v>
       </c>
-      <c r="O44" s="9" t="n">
+      <c r="O44" t="n">
         <v>8338</v>
       </c>
-      <c r="P44" s="9" t="n">
+      <c r="P44" t="n">
         <v>2660</v>
       </c>
-      <c r="Q44" s="9" t="n">
+      <c r="Q44" t="n">
         <v>2585</v>
       </c>
-      <c r="R44" s="9" t="n">
+      <c r="R44" t="n">
         <v>7900</v>
       </c>
-      <c r="S44" s="9" t="n">
+      <c r="S44" t="n">
         <v>4250</v>
       </c>
-      <c r="T44" s="9" t="n">
+      <c r="T44" t="n">
         <v>4828</v>
       </c>
-      <c r="U44" s="9" t="n">
+      <c r="U44" t="n">
         <v>5762</v>
       </c>
-      <c r="V44" s="9" t="n">
+      <c r="V44" t="n">
         <v>7006</v>
       </c>
-      <c r="W44" s="9" t="n">
+      <c r="W44" t="n">
         <v>5236</v>
       </c>
-      <c r="X44" s="9" t="n">
+      <c r="X44" t="n">
         <v>3366</v>
       </c>
-      <c r="Y44" s="10" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n">
+      <c r="B45" t="n">
         <v>5597</v>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="C45" t="n">
         <v>9730</v>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="D45" t="n">
         <v>4274</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" t="n">
         <v>23457</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" t="n">
         <v>4942</v>
       </c>
-      <c r="G45" s="9" t="n">
+      <c r="G45" t="n">
         <v>4587</v>
       </c>
-      <c r="H45" s="9" t="n">
+      <c r="H45" t="n">
         <v>16155</v>
       </c>
-      <c r="I45" s="9" t="n">
+      <c r="I45" t="n">
         <v>6017</v>
       </c>
-      <c r="J45" s="9" t="n">
+      <c r="J45" t="n">
         <v>4024</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" t="n">
         <v>7533</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" t="n">
         <v>2984</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" t="n">
         <v>5941</v>
       </c>
-      <c r="N45" s="9" t="n">
+      <c r="N45" t="n">
         <v>3513</v>
       </c>
-      <c r="O45" s="9" t="n">
+      <c r="O45" t="n">
         <v>8087</v>
       </c>
-      <c r="P45" s="9" t="n">
+      <c r="P45" t="n">
         <v>2892</v>
       </c>
-      <c r="Q45" s="9" t="n">
+      <c r="Q45" t="n">
         <v>2360</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" t="n">
         <v>8823</v>
       </c>
-      <c r="S45" s="9" t="n">
+      <c r="S45" t="n">
         <v>3711</v>
       </c>
-      <c r="T45" s="9" t="n">
+      <c r="T45" t="n">
         <v>4485</v>
       </c>
-      <c r="U45" s="9" t="n">
+      <c r="U45" t="n">
         <v>5474</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" t="n">
         <v>7782</v>
       </c>
-      <c r="W45" s="9" t="n">
+      <c r="W45" t="n">
         <v>5606</v>
       </c>
-      <c r="X45" s="9" t="n">
+      <c r="X45" t="n">
         <v>3594</v>
       </c>
-      <c r="Y45" s="10" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" t="n">
         <v>5028</v>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="C46" t="n">
         <v>9956</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" t="n">
         <v>4142</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" t="n">
         <v>22017</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" t="n">
         <v>4975</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" t="n">
         <v>4325</v>
       </c>
-      <c r="H46" s="9" t="n">
+      <c r="H46" t="n">
         <v>15219</v>
       </c>
-      <c r="I46" s="9" t="n">
+      <c r="I46" t="n">
         <v>6807</v>
       </c>
-      <c r="J46" s="9" t="n">
+      <c r="J46" t="n">
         <v>3984</v>
       </c>
-      <c r="K46" s="9" t="n">
+      <c r="K46" t="n">
         <v>7123</v>
       </c>
-      <c r="L46" s="9" t="n">
+      <c r="L46" t="n">
         <v>3277</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" t="n">
         <v>5603</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" t="n">
         <v>3711</v>
       </c>
-      <c r="O46" s="9" t="n">
+      <c r="O46" t="n">
         <v>7954</v>
       </c>
-      <c r="P46" s="9" t="n">
+      <c r="P46" t="n">
         <v>2923</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" t="n">
         <v>2514</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" t="n">
         <v>8235</v>
       </c>
-      <c r="S46" s="9" t="n">
+      <c r="S46" t="n">
         <v>3855</v>
       </c>
-      <c r="T46" s="9" t="n">
+      <c r="T46" t="n">
         <v>4617</v>
       </c>
-      <c r="U46" s="9" t="n">
+      <c r="U46" t="n">
         <v>5612</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" t="n">
         <v>7678</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" t="n">
         <v>5561</v>
       </c>
-      <c r="X46" s="9" t="n">
+      <c r="X46" t="n">
         <v>3376</v>
       </c>
-      <c r="Y46" s="10" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n">
+      <c r="B47" t="n">
         <v>4867</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" t="n">
         <v>10408</v>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D47" t="n">
         <v>4052</v>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" t="n">
         <v>23670</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" t="n">
         <v>4960</v>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="G47" t="n">
         <v>4469</v>
       </c>
-      <c r="H47" s="9" t="n">
+      <c r="H47" t="n">
         <v>15520</v>
       </c>
-      <c r="I47" s="9" t="n">
+      <c r="I47" t="n">
         <v>6200</v>
       </c>
-      <c r="J47" s="9" t="n">
+      <c r="J47" t="n">
         <v>3723</v>
       </c>
-      <c r="K47" s="9" t="n">
+      <c r="K47" t="n">
         <v>7400</v>
       </c>
-      <c r="L47" s="9" t="n">
+      <c r="L47" t="n">
         <v>3253</v>
       </c>
-      <c r="M47" s="9" t="n">
+      <c r="M47" t="n">
         <v>6092</v>
       </c>
-      <c r="N47" s="9" t="n">
+      <c r="N47" t="n">
         <v>3253</v>
       </c>
-      <c r="O47" s="9" t="n">
+      <c r="O47" t="n">
         <v>7831</v>
       </c>
-      <c r="P47" s="9" t="n">
+      <c r="P47" t="n">
         <v>2791</v>
       </c>
-      <c r="Q47" s="9" t="n">
+      <c r="Q47" t="n">
         <v>2377</v>
       </c>
-      <c r="R47" s="9" t="n">
+      <c r="R47" t="n">
         <v>8000</v>
       </c>
-      <c r="S47" s="9" t="n">
+      <c r="S47" t="n">
         <v>4218</v>
       </c>
-      <c r="T47" s="9" t="n">
+      <c r="T47" t="n">
         <v>4788</v>
       </c>
-      <c r="U47" s="9" t="n">
+      <c r="U47" t="n">
         <v>5113</v>
       </c>
-      <c r="V47" s="9" t="n">
+      <c r="V47" t="n">
         <v>7548</v>
       </c>
-      <c r="W47" s="9" t="n">
+      <c r="W47" t="n">
         <v>5538</v>
       </c>
-      <c r="X47" s="9" t="n">
+      <c r="X47" t="n">
         <v>3283</v>
       </c>
-      <c r="Y47" s="10" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" t="n">
         <v>5509</v>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C48" t="n">
         <v>9505</v>
       </c>
-      <c r="D48" s="9" t="n">
+      <c r="D48" t="n">
         <v>4460</v>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E48" t="n">
         <v>22738</v>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" t="n">
         <v>4879</v>
       </c>
-      <c r="G48" s="9" t="n">
+      <c r="G48" t="n">
         <v>4437</v>
       </c>
-      <c r="H48" s="9" t="n">
+      <c r="H48" t="n">
         <v>14161</v>
       </c>
-      <c r="I48" s="9" t="n">
+      <c r="I48" t="n">
         <v>6184</v>
       </c>
-      <c r="J48" s="9" t="n">
+      <c r="J48" t="n">
         <v>3529</v>
       </c>
-      <c r="K48" s="9" t="n">
+      <c r="K48" t="n">
         <v>7383</v>
       </c>
-      <c r="L48" s="9" t="n">
+      <c r="L48" t="n">
         <v>3306</v>
       </c>
-      <c r="M48" s="9" t="n">
+      <c r="M48" t="n">
         <v>5641</v>
       </c>
-      <c r="N48" s="9" t="n">
+      <c r="N48" t="n">
         <v>3244</v>
       </c>
-      <c r="O48" s="9" t="n">
+      <c r="O48" t="n">
         <v>8231</v>
       </c>
-      <c r="P48" s="9" t="n">
+      <c r="P48" t="n">
         <v>3016</v>
       </c>
-      <c r="Q48" s="9" t="n">
+      <c r="Q48" t="n">
         <v>2517</v>
       </c>
-      <c r="R48" s="9" t="n">
+      <c r="R48" t="n">
         <v>8014</v>
       </c>
-      <c r="S48" s="9" t="n">
+      <c r="S48" t="n">
         <v>3750</v>
       </c>
-      <c r="T48" s="9" t="n">
+      <c r="T48" t="n">
         <v>4995</v>
       </c>
-      <c r="U48" s="9" t="n">
+      <c r="U48" t="n">
         <v>5197</v>
       </c>
-      <c r="V48" s="9" t="n">
+      <c r="V48" t="n">
         <v>7064</v>
       </c>
-      <c r="W48" s="9" t="n">
+      <c r="W48" t="n">
         <v>5137</v>
       </c>
-      <c r="X48" s="9" t="n">
+      <c r="X48" t="n">
         <v>3647</v>
       </c>
-      <c r="Y48" s="10" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="B49" s="9" t="n">
+      <c r="B49" t="n">
         <v>5526</v>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" t="n">
         <v>9516</v>
       </c>
-      <c r="D49" s="9" t="n">
+      <c r="D49" t="n">
         <v>4316</v>
       </c>
-      <c r="E49" s="9" t="n">
+      <c r="E49" t="n">
         <v>20473</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" t="n">
         <v>5034</v>
       </c>
-      <c r="G49" s="9" t="n">
+      <c r="G49" t="n">
         <v>4340</v>
       </c>
-      <c r="H49" s="9" t="n">
+      <c r="H49" t="n">
         <v>15786</v>
       </c>
-      <c r="I49" s="9" t="n">
+      <c r="I49" t="n">
         <v>6818</v>
       </c>
-      <c r="J49" s="9" t="n">
+      <c r="J49" t="n">
         <v>3927</v>
       </c>
-      <c r="K49" s="9" t="n">
+      <c r="K49" t="n">
         <v>7419</v>
       </c>
-      <c r="L49" s="9" t="n">
+      <c r="L49" t="n">
         <v>3078</v>
       </c>
-      <c r="M49" s="9" t="n">
+      <c r="M49" t="n">
         <v>5499</v>
       </c>
-      <c r="N49" s="9" t="n">
+      <c r="N49" t="n">
         <v>3543</v>
       </c>
-      <c r="O49" s="9" t="n">
+      <c r="O49" t="n">
         <v>7866</v>
       </c>
-      <c r="P49" s="9" t="n">
+      <c r="P49" t="n">
         <v>2945</v>
       </c>
-      <c r="Q49" s="9" t="n">
+      <c r="Q49" t="n">
         <v>2321</v>
       </c>
-      <c r="R49" s="9" t="n">
+      <c r="R49" t="n">
         <v>8805</v>
       </c>
-      <c r="S49" s="9" t="n">
+      <c r="S49" t="n">
         <v>4162</v>
       </c>
-      <c r="T49" s="9" t="n">
+      <c r="T49" t="n">
         <v>5044</v>
       </c>
-      <c r="U49" s="9" t="n">
+      <c r="U49" t="n">
         <v>5415</v>
       </c>
-      <c r="V49" s="9" t="n">
+      <c r="V49" t="n">
         <v>7657</v>
       </c>
-      <c r="W49" s="9" t="n">
+      <c r="W49" t="n">
         <v>5492</v>
       </c>
-      <c r="X49" s="9" t="n">
+      <c r="X49" t="n">
         <v>3276</v>
       </c>
-      <c r="Y49" s="10" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B50" t="n">
         <v>5078</v>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C50" t="n">
         <v>10000</v>
       </c>
-      <c r="D50" s="9" t="n">
+      <c r="D50" t="n">
         <v>4353</v>
       </c>
-      <c r="E50" s="9" t="n">
+      <c r="E50" t="n">
         <v>20894</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F50" t="n">
         <v>4441</v>
       </c>
-      <c r="G50" s="9" t="n">
+      <c r="G50" t="n">
         <v>4340</v>
       </c>
-      <c r="H50" s="9" t="n">
+      <c r="H50" t="n">
         <v>14715</v>
       </c>
-      <c r="I50" s="9" t="n">
+      <c r="I50" t="n">
         <v>6105</v>
       </c>
-      <c r="J50" s="9" t="n">
+      <c r="J50" t="n">
         <v>3978</v>
       </c>
-      <c r="K50" s="9" t="n">
+      <c r="K50" t="n">
         <v>8054</v>
       </c>
-      <c r="L50" s="9" t="n">
+      <c r="L50" t="n">
         <v>3435</v>
       </c>
-      <c r="M50" s="9" t="n">
+      <c r="M50" t="n">
         <v>5507</v>
       </c>
-      <c r="N50" s="9" t="n">
+      <c r="N50" t="n">
         <v>3708</v>
       </c>
-      <c r="O50" s="9" t="n">
+      <c r="O50" t="n">
         <v>8050</v>
       </c>
-      <c r="P50" s="9" t="n">
+      <c r="P50" t="n">
         <v>2690</v>
       </c>
-      <c r="Q50" s="9" t="n">
+      <c r="Q50" t="n">
         <v>2353</v>
       </c>
-      <c r="R50" s="9" t="n">
+      <c r="R50" t="n">
         <v>8260</v>
       </c>
-      <c r="S50" s="9" t="n">
+      <c r="S50" t="n">
         <v>3977</v>
       </c>
-      <c r="T50" s="9" t="n">
+      <c r="T50" t="n">
         <v>4517</v>
       </c>
-      <c r="U50" s="9" t="n">
+      <c r="U50" t="n">
         <v>5917</v>
       </c>
-      <c r="V50" s="9" t="n">
+      <c r="V50" t="n">
         <v>7825</v>
       </c>
-      <c r="W50" s="9" t="n">
+      <c r="W50" t="n">
         <v>5578</v>
       </c>
-      <c r="X50" s="9" t="n">
+      <c r="X50" t="n">
         <v>3549</v>
       </c>
-      <c r="Y50" s="10" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
+      <c r="B51" t="n">
         <v>5095</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" t="n">
         <v>10047</v>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="D51" t="n">
         <v>4434</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E51" t="n">
         <v>23401</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" t="n">
         <v>4448</v>
       </c>
-      <c r="G51" s="9" t="n">
+      <c r="G51" t="n">
         <v>4326</v>
       </c>
-      <c r="H51" s="9" t="n">
+      <c r="H51" t="n">
         <v>14356</v>
       </c>
-      <c r="I51" s="9" t="n">
+      <c r="I51" t="n">
         <v>6935</v>
       </c>
-      <c r="J51" s="9" t="n">
+      <c r="J51" t="n">
         <v>3602</v>
       </c>
-      <c r="K51" s="9" t="n">
+      <c r="K51" t="n">
         <v>7796</v>
       </c>
-      <c r="L51" s="9" t="n">
+      <c r="L51" t="n">
         <v>3183</v>
       </c>
-      <c r="M51" s="9" t="n">
+      <c r="M51" t="n">
         <v>5743</v>
       </c>
-      <c r="N51" s="9" t="n">
+      <c r="N51" t="n">
         <v>3642</v>
       </c>
-      <c r="O51" s="9" t="n">
+      <c r="O51" t="n">
         <v>7963</v>
       </c>
-      <c r="P51" s="9" t="n">
+      <c r="P51" t="n">
         <v>2820</v>
       </c>
-      <c r="Q51" s="9" t="n">
+      <c r="Q51" t="n">
         <v>2559</v>
       </c>
-      <c r="R51" s="9" t="n">
+      <c r="R51" t="n">
         <v>8246</v>
       </c>
-      <c r="S51" s="9" t="n">
+      <c r="S51" t="n">
         <v>4250</v>
       </c>
-      <c r="T51" s="9" t="n">
+      <c r="T51" t="n">
         <v>4741</v>
       </c>
-      <c r="U51" s="9" t="n">
+      <c r="U51" t="n">
         <v>5679</v>
       </c>
-      <c r="V51" s="9" t="n">
+      <c r="V51" t="n">
         <v>7599</v>
       </c>
-      <c r="W51" s="9" t="n">
+      <c r="W51" t="n">
         <v>4870</v>
       </c>
-      <c r="X51" s="9" t="n">
+      <c r="X51" t="n">
         <v>3254</v>
       </c>
-      <c r="Y51" s="10" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n">
+      <c r="B52" t="n">
         <v>5145</v>
       </c>
-      <c r="C52" s="9" t="n">
+      <c r="C52" t="n">
         <v>9269</v>
       </c>
-      <c r="D52" s="9" t="n">
+      <c r="D52" t="n">
         <v>4028</v>
       </c>
-      <c r="E52" s="9" t="n">
+      <c r="E52" t="n">
         <v>20491</v>
       </c>
-      <c r="F52" s="9" t="n">
+      <c r="F52" t="n">
         <v>4703</v>
       </c>
-      <c r="G52" s="9" t="n">
+      <c r="G52" t="n">
         <v>4221</v>
       </c>
-      <c r="H52" s="9" t="n">
+      <c r="H52" t="n">
         <v>14062</v>
       </c>
-      <c r="I52" s="9" t="n">
+      <c r="I52" t="n">
         <v>6228</v>
       </c>
-      <c r="J52" s="9" t="n">
+      <c r="J52" t="n">
         <v>4066</v>
       </c>
-      <c r="K52" s="9" t="n">
+      <c r="K52" t="n">
         <v>7108</v>
       </c>
-      <c r="L52" s="9" t="n">
+      <c r="L52" t="n">
         <v>3183</v>
       </c>
-      <c r="M52" s="9" t="n">
+      <c r="M52" t="n">
         <v>6070</v>
       </c>
-      <c r="N52" s="9" t="n">
+      <c r="N52" t="n">
         <v>3558</v>
       </c>
-      <c r="O52" s="9" t="n">
+      <c r="O52" t="n">
         <v>8255</v>
       </c>
-      <c r="P52" s="9" t="n">
+      <c r="P52" t="n">
         <v>2930</v>
       </c>
-      <c r="Q52" s="9" t="n">
+      <c r="Q52" t="n">
         <v>2655</v>
       </c>
-      <c r="R52" s="9" t="n">
+      <c r="R52" t="n">
         <v>8347</v>
       </c>
-      <c r="S52" s="9" t="n">
+      <c r="S52" t="n">
         <v>4311</v>
       </c>
-      <c r="T52" s="9" t="n">
+      <c r="T52" t="n">
         <v>4858</v>
       </c>
-      <c r="U52" s="9" t="n">
+      <c r="U52" t="n">
         <v>5095</v>
       </c>
-      <c r="V52" s="9" t="n">
+      <c r="V52" t="n">
         <v>8035</v>
       </c>
-      <c r="W52" s="9" t="n">
+      <c r="W52" t="n">
         <v>5091</v>
       </c>
-      <c r="X52" s="9" t="n">
+      <c r="X52" t="n">
         <v>3297</v>
       </c>
-      <c r="Y52" s="10" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="B53" s="9" t="n">
+      <c r="B53" t="n">
         <v>5331</v>
       </c>
-      <c r="C53" s="9" t="n">
+      <c r="C53" t="n">
         <v>10276</v>
       </c>
-      <c r="D53" s="9" t="n">
+      <c r="D53" t="n">
         <v>4419</v>
       </c>
-      <c r="E53" s="9" t="n">
+      <c r="E53" t="n">
         <v>22517</v>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="F53" t="n">
         <v>5014</v>
       </c>
-      <c r="G53" s="9" t="n">
+      <c r="G53" t="n">
         <v>4461</v>
       </c>
-      <c r="H53" s="9" t="n">
+      <c r="H53" t="n">
         <v>13999</v>
       </c>
-      <c r="I53" s="9" t="n">
+      <c r="I53" t="n">
         <v>6692</v>
       </c>
-      <c r="J53" s="9" t="n">
+      <c r="J53" t="n">
         <v>4027</v>
       </c>
-      <c r="K53" s="9" t="n">
+      <c r="K53" t="n">
         <v>7233</v>
       </c>
-      <c r="L53" s="9" t="n">
+      <c r="L53" t="n">
         <v>3124</v>
       </c>
-      <c r="M53" s="9" t="n">
+      <c r="M53" t="n">
         <v>5443</v>
       </c>
-      <c r="N53" s="9" t="n">
+      <c r="N53" t="n">
         <v>3593</v>
       </c>
-      <c r="O53" s="9" t="n">
+      <c r="O53" t="n">
         <v>7570</v>
       </c>
-      <c r="P53" s="9" t="n">
+      <c r="P53" t="n">
         <v>2700</v>
       </c>
-      <c r="Q53" s="9" t="n">
+      <c r="Q53" t="n">
         <v>2440</v>
       </c>
-      <c r="R53" s="9" t="n">
+      <c r="R53" t="n">
         <v>7956</v>
       </c>
-      <c r="S53" s="9" t="n">
+      <c r="S53" t="n">
         <v>4108</v>
       </c>
-      <c r="T53" s="9" t="n">
+      <c r="T53" t="n">
         <v>5020</v>
       </c>
-      <c r="U53" s="9" t="n">
+      <c r="U53" t="n">
         <v>5880</v>
       </c>
-      <c r="V53" s="9" t="n">
+      <c r="V53" t="n">
         <v>6933</v>
       </c>
-      <c r="W53" s="9" t="n">
+      <c r="W53" t="n">
         <v>5306</v>
       </c>
-      <c r="X53" s="9" t="n">
+      <c r="X53" t="n">
         <v>3238</v>
       </c>
-      <c r="Y53" s="10" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B54" t="n">
         <v>4869</v>
       </c>
-      <c r="C54" s="9" t="n">
+      <c r="C54" t="n">
         <v>9885</v>
       </c>
-      <c r="D54" s="9" t="n">
+      <c r="D54" t="n">
         <v>4088</v>
       </c>
-      <c r="E54" s="9" t="n">
+      <c r="E54" t="n">
         <v>23189</v>
       </c>
-      <c r="F54" s="9" t="n">
+      <c r="F54" t="n">
         <v>4715</v>
       </c>
-      <c r="G54" s="9" t="n">
+      <c r="G54" t="n">
         <v>4496</v>
       </c>
-      <c r="H54" s="9" t="n">
+      <c r="H54" t="n">
         <v>15623</v>
       </c>
-      <c r="I54" s="9" t="n">
+      <c r="I54" t="n">
         <v>6020</v>
       </c>
-      <c r="J54" s="9" t="n">
+      <c r="J54" t="n">
         <v>3977</v>
       </c>
-      <c r="K54" s="9" t="n">
+      <c r="K54" t="n">
         <v>7175</v>
       </c>
-      <c r="L54" s="9" t="n">
+      <c r="L54" t="n">
         <v>3428</v>
       </c>
-      <c r="M54" s="9" t="n">
+      <c r="M54" t="n">
         <v>5496</v>
       </c>
-      <c r="N54" s="9" t="n">
+      <c r="N54" t="n">
         <v>3588</v>
       </c>
-      <c r="O54" s="9" t="n">
+      <c r="O54" t="n">
         <v>7448</v>
       </c>
-      <c r="P54" s="9" t="n">
+      <c r="P54" t="n">
         <v>2964</v>
       </c>
-      <c r="Q54" s="9" t="n">
+      <c r="Q54" t="n">
         <v>2528</v>
       </c>
-      <c r="R54" s="9" t="n">
+      <c r="R54" t="n">
         <v>8626</v>
       </c>
-      <c r="S54" s="9" t="n">
+      <c r="S54" t="n">
         <v>3730</v>
       </c>
-      <c r="T54" s="9" t="n">
+      <c r="T54" t="n">
         <v>4504</v>
       </c>
-      <c r="U54" s="9" t="n">
+      <c r="U54" t="n">
         <v>5072</v>
       </c>
-      <c r="V54" s="9" t="n">
+      <c r="V54" t="n">
         <v>7686</v>
       </c>
-      <c r="W54" s="9" t="n">
+      <c r="W54" t="n">
         <v>5357</v>
       </c>
-      <c r="X54" s="9" t="n">
+      <c r="X54" t="n">
         <v>3310</v>
       </c>
-      <c r="Y54" s="10" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B55" s="9" t="n">
+      <c r="B55" t="n">
         <v>5168</v>
       </c>
-      <c r="C55" s="9" t="n">
+      <c r="C55" t="n">
         <v>10267</v>
       </c>
-      <c r="D55" s="9" t="n">
+      <c r="D55" t="n">
         <v>4016</v>
       </c>
-      <c r="E55" s="9" t="n">
+      <c r="E55" t="n">
         <v>22237</v>
       </c>
-      <c r="F55" s="9" t="n">
+      <c r="F55" t="n">
         <v>5053</v>
       </c>
-      <c r="G55" s="9" t="n">
+      <c r="G55" t="n">
         <v>4648</v>
       </c>
-      <c r="H55" s="9" t="n">
+      <c r="H55" t="n">
         <v>15864</v>
       </c>
-      <c r="I55" s="9" t="n">
+      <c r="I55" t="n">
         <v>6325</v>
       </c>
-      <c r="J55" s="9" t="n">
+      <c r="J55" t="n">
         <v>3678</v>
       </c>
-      <c r="K55" s="9" t="n">
+      <c r="K55" t="n">
         <v>7725</v>
       </c>
-      <c r="L55" s="9" t="n">
+      <c r="L55" t="n">
         <v>3028</v>
       </c>
-      <c r="M55" s="9" t="n">
+      <c r="M55" t="n">
         <v>5916</v>
       </c>
-      <c r="N55" s="9" t="n">
+      <c r="N55" t="n">
         <v>3641</v>
       </c>
-      <c r="O55" s="9" t="n">
+      <c r="O55" t="n">
         <v>7494</v>
       </c>
-      <c r="P55" s="9" t="n">
+      <c r="P55" t="n">
         <v>2687</v>
       </c>
-      <c r="Q55" s="9" t="n">
+      <c r="Q55" t="n">
         <v>2365</v>
       </c>
-      <c r="R55" s="9" t="n">
+      <c r="R55" t="n">
         <v>8264</v>
       </c>
-      <c r="S55" s="9" t="n">
+      <c r="S55" t="n">
         <v>4132</v>
       </c>
-      <c r="T55" s="9" t="n">
+      <c r="T55" t="n">
         <v>4716</v>
       </c>
-      <c r="U55" s="9" t="n">
+      <c r="U55" t="n">
         <v>5759</v>
       </c>
-      <c r="V55" s="9" t="n">
+      <c r="V55" t="n">
         <v>8048</v>
       </c>
-      <c r="W55" s="9" t="n">
+      <c r="W55" t="n">
         <v>5218</v>
       </c>
-      <c r="X55" s="9" t="n">
+      <c r="X55" t="n">
         <v>3223</v>
       </c>
-      <c r="Y55" s="10" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n">
+      <c r="B56" t="n">
         <v>5451</v>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="C56" t="n">
         <v>9161</v>
       </c>
-      <c r="D56" s="9" t="n">
+      <c r="D56" t="n">
         <v>4104</v>
       </c>
-      <c r="E56" s="9" t="n">
+      <c r="E56" t="n">
         <v>22118</v>
       </c>
-      <c r="F56" s="9" t="n">
+      <c r="F56" t="n">
         <v>5015</v>
       </c>
-      <c r="G56" s="9" t="n">
+      <c r="G56" t="n">
         <v>4770</v>
       </c>
-      <c r="H56" s="9" t="n">
+      <c r="H56" t="n">
         <v>13994</v>
       </c>
-      <c r="I56" s="9" t="n">
+      <c r="I56" t="n">
         <v>6788</v>
       </c>
-      <c r="J56" s="9" t="n">
+      <c r="J56" t="n">
         <v>3946</v>
       </c>
-      <c r="K56" s="9" t="n">
+      <c r="K56" t="n">
         <v>7911</v>
       </c>
-      <c r="L56" s="9" t="n">
+      <c r="L56" t="n">
         <v>3295</v>
       </c>
-      <c r="M56" s="9" t="n">
+      <c r="M56" t="n">
         <v>5827</v>
       </c>
-      <c r="N56" s="9" t="n">
+      <c r="N56" t="n">
         <v>3505</v>
       </c>
-      <c r="O56" s="9" t="n">
+      <c r="O56" t="n">
         <v>7909</v>
       </c>
-      <c r="P56" s="9" t="n">
+      <c r="P56" t="n">
         <v>2986</v>
       </c>
-      <c r="Q56" s="9" t="n">
+      <c r="Q56" t="n">
         <v>2633</v>
       </c>
-      <c r="R56" s="9" t="n">
+      <c r="R56" t="n">
         <v>7891</v>
       </c>
-      <c r="S56" s="9" t="n">
+      <c r="S56" t="n">
         <v>3842</v>
       </c>
-      <c r="T56" s="9" t="n">
+      <c r="T56" t="n">
         <v>4617</v>
       </c>
-      <c r="U56" s="9" t="n">
+      <c r="U56" t="n">
         <v>5180</v>
       </c>
-      <c r="V56" s="9" t="n">
+      <c r="V56" t="n">
         <v>7116</v>
       </c>
-      <c r="W56" s="9" t="n">
+      <c r="W56" t="n">
         <v>5375</v>
       </c>
-      <c r="X56" s="9" t="n">
+      <c r="X56" t="n">
         <v>3591</v>
       </c>
-      <c r="Y56" s="10" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n">
+      <c r="B57" t="n">
         <v>4827</v>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C57" t="n">
         <v>10514</v>
       </c>
-      <c r="D57" s="9" t="n">
+      <c r="D57" t="n">
         <v>4152</v>
       </c>
-      <c r="E57" s="9" t="n">
+      <c r="E57" t="n">
         <v>22271</v>
       </c>
-      <c r="F57" s="9" t="n">
+      <c r="F57" t="n">
         <v>4820</v>
       </c>
-      <c r="G57" s="9" t="n">
+      <c r="G57" t="n">
         <v>4384</v>
       </c>
-      <c r="H57" s="9" t="n">
+      <c r="H57" t="n">
         <v>14539</v>
       </c>
-      <c r="I57" s="9" t="n">
+      <c r="I57" t="n">
         <v>6379</v>
       </c>
-      <c r="J57" s="9" t="n">
+      <c r="J57" t="n">
         <v>3779</v>
       </c>
-      <c r="K57" s="9" t="n">
+      <c r="K57" t="n">
         <v>7283</v>
       </c>
-      <c r="L57" s="9" t="n">
+      <c r="L57" t="n">
         <v>3243</v>
       </c>
-      <c r="M57" s="9" t="n">
+      <c r="M57" t="n">
         <v>5592</v>
       </c>
-      <c r="N57" s="9" t="n">
+      <c r="N57" t="n">
         <v>3622</v>
       </c>
-      <c r="O57" s="9" t="n">
+      <c r="O57" t="n">
         <v>7703</v>
       </c>
-      <c r="P57" s="9" t="n">
+      <c r="P57" t="n">
         <v>2608</v>
       </c>
-      <c r="Q57" s="9" t="n">
+      <c r="Q57" t="n">
         <v>2448</v>
       </c>
-      <c r="R57" s="9" t="n">
+      <c r="R57" t="n">
         <v>9150</v>
       </c>
-      <c r="S57" s="9" t="n">
+      <c r="S57" t="n">
         <v>3800</v>
       </c>
-      <c r="T57" s="9" t="n">
+      <c r="T57" t="n">
         <v>4969</v>
       </c>
-      <c r="U57" s="9" t="n">
+      <c r="U57" t="n">
         <v>5852</v>
       </c>
-      <c r="V57" s="9" t="n">
+      <c r="V57" t="n">
         <v>8097</v>
       </c>
-      <c r="W57" s="9" t="n">
+      <c r="W57" t="n">
         <v>5180</v>
       </c>
-      <c r="X57" s="9" t="n">
+      <c r="X57" t="n">
         <v>3589</v>
       </c>
-      <c r="Y57" s="10" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n">
+      <c r="B58" t="n">
         <v>5612</v>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C58" t="n">
         <v>9417</v>
       </c>
-      <c r="D58" s="9" t="n">
+      <c r="D58" t="n">
         <v>4148</v>
       </c>
-      <c r="E58" s="9" t="n">
+      <c r="E58" t="n">
         <v>22498</v>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" t="n">
         <v>5054</v>
       </c>
-      <c r="G58" s="9" t="n">
+      <c r="G58" t="n">
         <v>4624</v>
       </c>
-      <c r="H58" s="9" t="n">
+      <c r="H58" t="n">
         <v>16150</v>
       </c>
-      <c r="I58" s="9" t="n">
+      <c r="I58" t="n">
         <v>6981</v>
       </c>
-      <c r="J58" s="9" t="n">
+      <c r="J58" t="n">
         <v>3730</v>
       </c>
-      <c r="K58" s="9" t="n">
+      <c r="K58" t="n">
         <v>8045</v>
       </c>
-      <c r="L58" s="9" t="n">
+      <c r="L58" t="n">
         <v>3281</v>
       </c>
-      <c r="M58" s="9" t="n">
+      <c r="M58" t="n">
         <v>5338</v>
       </c>
-      <c r="N58" s="9" t="n">
+      <c r="N58" t="n">
         <v>3744</v>
       </c>
-      <c r="O58" s="9" t="n">
+      <c r="O58" t="n">
         <v>7851</v>
       </c>
-      <c r="P58" s="9" t="n">
+      <c r="P58" t="n">
         <v>2766</v>
       </c>
-      <c r="Q58" s="9" t="n">
+      <c r="Q58" t="n">
         <v>2356</v>
       </c>
-      <c r="R58" s="9" t="n">
+      <c r="R58" t="n">
         <v>9091</v>
       </c>
-      <c r="S58" s="9" t="n">
+      <c r="S58" t="n">
         <v>3826</v>
       </c>
-      <c r="T58" s="9" t="n">
+      <c r="T58" t="n">
         <v>4610</v>
       </c>
-      <c r="U58" s="9" t="n">
+      <c r="U58" t="n">
         <v>5450</v>
       </c>
-      <c r="V58" s="9" t="n">
+      <c r="V58" t="n">
         <v>7334</v>
       </c>
-      <c r="W58" s="9" t="n">
+      <c r="W58" t="n">
         <v>5254</v>
       </c>
-      <c r="X58" s="9" t="n">
+      <c r="X58" t="n">
         <v>3587</v>
       </c>
-      <c r="Y58" s="10" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n">
+      <c r="B59" t="n">
         <v>5261</v>
       </c>
-      <c r="C59" s="9" t="n">
+      <c r="C59" t="n">
         <v>9099</v>
       </c>
-      <c r="D59" s="9" t="n">
+      <c r="D59" t="n">
         <v>4451</v>
       </c>
-      <c r="E59" s="9" t="n">
+      <c r="E59" t="n">
         <v>23026</v>
       </c>
-      <c r="F59" s="9" t="n">
+      <c r="F59" t="n">
         <v>4462</v>
       </c>
-      <c r="G59" s="9" t="n">
+      <c r="G59" t="n">
         <v>4292</v>
       </c>
-      <c r="H59" s="9" t="n">
+      <c r="H59" t="n">
         <v>15295</v>
       </c>
-      <c r="I59" s="9" t="n">
+      <c r="I59" t="n">
         <v>6118</v>
       </c>
-      <c r="J59" s="9" t="n">
+      <c r="J59" t="n">
         <v>3966</v>
       </c>
-      <c r="K59" s="9" t="n">
+      <c r="K59" t="n">
         <v>7250</v>
       </c>
-      <c r="L59" s="9" t="n">
+      <c r="L59" t="n">
         <v>3102</v>
       </c>
-      <c r="M59" s="9" t="n">
+      <c r="M59" t="n">
         <v>5931</v>
       </c>
-      <c r="N59" s="9" t="n">
+      <c r="N59" t="n">
         <v>3717</v>
       </c>
-      <c r="O59" s="9" t="n">
+      <c r="O59" t="n">
         <v>8105</v>
       </c>
-      <c r="P59" s="9" t="n">
+      <c r="P59" t="n">
         <v>2825</v>
       </c>
-      <c r="Q59" s="9" t="n">
+      <c r="Q59" t="n">
         <v>2374</v>
       </c>
-      <c r="R59" s="9" t="n">
+      <c r="R59" t="n">
         <v>8114</v>
       </c>
-      <c r="S59" s="9" t="n">
+      <c r="S59" t="n">
         <v>3738</v>
       </c>
-      <c r="T59" s="9" t="n">
+      <c r="T59" t="n">
         <v>4705</v>
       </c>
-      <c r="U59" s="9" t="n">
+      <c r="U59" t="n">
         <v>5206</v>
       </c>
-      <c r="V59" s="9" t="n">
+      <c r="V59" t="n">
         <v>7544</v>
       </c>
-      <c r="W59" s="9" t="n">
+      <c r="W59" t="n">
         <v>5406</v>
       </c>
-      <c r="X59" s="9" t="n">
+      <c r="X59" t="n">
         <v>3532</v>
       </c>
-      <c r="Y59" s="10" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n">
+      <c r="B60" t="n">
         <v>5400</v>
       </c>
-      <c r="C60" s="9" t="n">
+      <c r="C60" t="n">
         <v>9411</v>
       </c>
-      <c r="D60" s="9" t="n">
+      <c r="D60" t="n">
         <v>4068</v>
       </c>
-      <c r="E60" s="9" t="n">
+      <c r="E60" t="n">
         <v>20717</v>
       </c>
-      <c r="F60" s="9" t="n">
+      <c r="F60" t="n">
         <v>4829</v>
       </c>
-      <c r="G60" s="9" t="n">
+      <c r="G60" t="n">
         <v>4278</v>
       </c>
-      <c r="H60" s="9" t="n">
+      <c r="H60" t="n">
         <v>15303</v>
       </c>
-      <c r="I60" s="9" t="n">
+      <c r="I60" t="n">
         <v>6926</v>
       </c>
-      <c r="J60" s="9" t="n">
+      <c r="J60" t="n">
         <v>3687</v>
       </c>
-      <c r="K60" s="9" t="n">
+      <c r="K60" t="n">
         <v>7604</v>
       </c>
-      <c r="L60" s="9" t="n">
+      <c r="L60" t="n">
         <v>3089</v>
       </c>
-      <c r="M60" s="9" t="n">
+      <c r="M60" t="n">
         <v>5455</v>
       </c>
-      <c r="N60" s="9" t="n">
+      <c r="N60" t="n">
         <v>3393</v>
       </c>
-      <c r="O60" s="9" t="n">
+      <c r="O60" t="n">
         <v>8354</v>
       </c>
-      <c r="P60" s="9" t="n">
+      <c r="P60" t="n">
         <v>2866</v>
       </c>
-      <c r="Q60" s="9" t="n">
+      <c r="Q60" t="n">
         <v>2632</v>
       </c>
-      <c r="R60" s="9" t="n">
+      <c r="R60" t="n">
         <v>8814</v>
       </c>
-      <c r="S60" s="9" t="n">
+      <c r="S60" t="n">
         <v>3855</v>
       </c>
-      <c r="T60" s="9" t="n">
+      <c r="T60" t="n">
         <v>4815</v>
       </c>
-      <c r="U60" s="9" t="n">
+      <c r="U60" t="n">
         <v>5770</v>
       </c>
-      <c r="V60" s="9" t="n">
+      <c r="V60" t="n">
         <v>7804</v>
       </c>
-      <c r="W60" s="9" t="n">
+      <c r="W60" t="n">
         <v>5562</v>
       </c>
-      <c r="X60" s="9" t="n">
+      <c r="X60" t="n">
         <v>3563</v>
       </c>
-      <c r="Y60" s="10" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="B61" s="9" t="n">
+      <c r="B61" t="n">
         <v>4812</v>
       </c>
-      <c r="C61" s="9" t="n">
+      <c r="C61" t="n">
         <v>9954</v>
       </c>
-      <c r="D61" s="9" t="n">
+      <c r="D61" t="n">
         <v>3998</v>
       </c>
-      <c r="E61" s="9" t="n">
+      <c r="E61" t="n">
         <v>23438</v>
       </c>
-      <c r="F61" s="9" t="n">
+      <c r="F61" t="n">
         <v>4616</v>
       </c>
-      <c r="G61" s="9" t="n">
+      <c r="G61" t="n">
         <v>4256</v>
       </c>
-      <c r="H61" s="9" t="n">
+      <c r="H61" t="n">
         <v>13895</v>
       </c>
-      <c r="I61" s="9" t="n">
+      <c r="I61" t="n">
         <v>6008</v>
       </c>
-      <c r="J61" s="9" t="n">
+      <c r="J61" t="n">
         <v>3704</v>
       </c>
-      <c r="K61" s="9" t="n">
+      <c r="K61" t="n">
         <v>7520</v>
       </c>
-      <c r="L61" s="9" t="n">
+      <c r="L61" t="n">
         <v>3360</v>
       </c>
-      <c r="M61" s="9" t="n">
+      <c r="M61" t="n">
         <v>5927</v>
       </c>
-      <c r="N61" s="9" t="n">
+      <c r="N61" t="n">
         <v>3550</v>
       </c>
-      <c r="O61" s="9" t="n">
+      <c r="O61" t="n">
         <v>8161</v>
       </c>
-      <c r="P61" s="9" t="n">
+      <c r="P61" t="n">
         <v>2798</v>
       </c>
-      <c r="Q61" s="9" t="n">
+      <c r="Q61" t="n">
         <v>2349</v>
       </c>
-      <c r="R61" s="9" t="n">
+      <c r="R61" t="n">
         <v>8309</v>
       </c>
-      <c r="S61" s="9" t="n">
+      <c r="S61" t="n">
         <v>4062</v>
       </c>
-      <c r="T61" s="9" t="n">
+      <c r="T61" t="n">
         <v>5018</v>
       </c>
-      <c r="U61" s="9" t="n">
+      <c r="U61" t="n">
         <v>5346</v>
       </c>
-      <c r="V61" s="9" t="n">
+      <c r="V61" t="n">
         <v>7833</v>
       </c>
-      <c r="W61" s="9" t="n">
+      <c r="W61" t="n">
         <v>4974</v>
       </c>
-      <c r="X61" s="9" t="n">
+      <c r="X61" t="n">
         <v>3394</v>
       </c>
-      <c r="Y61" s="10" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Referensi Industri Indonesia</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="B62" s="12" t="n">
+      <c r="B62" t="n">
         <v>4896</v>
       </c>
-      <c r="C62" s="12" t="n">
+      <c r="C62" t="n">
         <v>7984</v>
       </c>
-      <c r="D62" s="12" t="n">
+      <c r="D62" t="n">
         <v>4039</v>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="E62" t="n">
         <v>8023</v>
       </c>
-      <c r="F62" s="12" t="n">
+      <c r="F62" t="n">
         <v>4764</v>
       </c>
-      <c r="G62" s="12" t="n">
+      <c r="G62" t="n">
         <v>4168</v>
       </c>
-      <c r="H62" s="12" t="n">
+      <c r="H62" t="n">
         <v>8149</v>
       </c>
-      <c r="I62" s="12" t="n">
+      <c r="I62" t="n">
         <v>7908</v>
       </c>
-      <c r="J62" s="12" t="n">
+      <c r="J62" t="n">
         <v>3637</v>
       </c>
-      <c r="K62" s="12" t="n">
+      <c r="K62" t="n">
         <v>8637</v>
       </c>
-      <c r="L62" s="12" t="n">
+      <c r="L62" t="n">
         <v>3202</v>
       </c>
-      <c r="M62" s="12" t="n">
+      <c r="M62" t="n">
         <v>8201</v>
       </c>
-      <c r="N62" s="12" t="n">
+      <c r="N62" t="n">
         <v>3582</v>
       </c>
-      <c r="O62" s="12" t="n">
+      <c r="O62" t="n">
         <v>8038</v>
       </c>
-      <c r="P62" s="12" t="n">
+      <c r="P62" t="n">
         <v>2830</v>
       </c>
-      <c r="Q62" s="12" t="n">
+      <c r="Q62" t="n">
         <v>2386</v>
       </c>
-      <c r="R62" s="12" t="n">
+      <c r="R62" t="n">
         <v>8059</v>
       </c>
-      <c r="S62" s="12" t="n">
+      <c r="S62" t="n">
         <v>4006</v>
       </c>
-      <c r="T62" s="12" t="n">
+      <c r="T62" t="n">
         <v>5148</v>
       </c>
-      <c r="U62" s="12" t="n">
+      <c r="U62" t="n">
         <v>5211</v>
       </c>
-      <c r="V62" s="12" t="n">
+      <c r="V62" t="n">
         <v>7515</v>
       </c>
-      <c r="W62" s="12" t="n">
+      <c r="W62" t="n">
         <v>4933</v>
       </c>
-      <c r="X62" s="12" t="n">
+      <c r="X62" t="n">
         <v>3332</v>
       </c>
-      <c r="Y62" s="12" t="n">
+      <c r="Y62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="B63" s="14" t="n">
+      <c r="B63" t="n">
         <v>4837</v>
       </c>
-      <c r="C63" s="14" t="n">
+      <c r="C63" t="n">
         <v>7699</v>
       </c>
-      <c r="D63" s="14" t="n">
+      <c r="D63" t="n">
         <v>3848</v>
       </c>
-      <c r="E63" s="14" t="n">
+      <c r="E63" t="n">
         <v>8075</v>
       </c>
-      <c r="F63" s="14" t="n">
+      <c r="F63" t="n">
         <v>4957</v>
       </c>
-      <c r="G63" s="14" t="n">
+      <c r="G63" t="n">
         <v>4289</v>
       </c>
-      <c r="H63" s="14" t="n">
+      <c r="H63" t="n">
         <v>7652</v>
       </c>
-      <c r="I63" s="14" t="n">
+      <c r="I63" t="n">
         <v>8108</v>
       </c>
-      <c r="J63" s="14" t="n">
+      <c r="J63" t="n">
         <v>3497</v>
       </c>
-      <c r="K63" s="14" t="n">
+      <c r="K63" t="n">
         <v>8124</v>
       </c>
-      <c r="L63" s="14" t="n">
+      <c r="L63" t="n">
         <v>3339</v>
       </c>
-      <c r="M63" s="14" t="n">
+      <c r="M63" t="n">
         <v>8322</v>
       </c>
-      <c r="N63" s="14" t="n">
+      <c r="N63" t="n">
         <v>3469</v>
       </c>
-      <c r="O63" s="14" t="n">
+      <c r="O63" t="n">
         <v>8143</v>
       </c>
-      <c r="P63" s="14" t="n">
+      <c r="P63" t="n">
         <v>2953</v>
       </c>
-      <c r="Q63" s="14" t="n">
+      <c r="Q63" t="n">
         <v>2455</v>
       </c>
-      <c r="R63" s="14" t="n">
+      <c r="R63" t="n">
         <v>7789</v>
       </c>
-      <c r="S63" s="14" t="n">
+      <c r="S63" t="n">
         <v>4139</v>
       </c>
-      <c r="T63" s="14" t="n">
+      <c r="T63" t="n">
         <v>5186</v>
       </c>
-      <c r="U63" s="14" t="n">
+      <c r="U63" t="n">
         <v>5465</v>
       </c>
-      <c r="V63" s="14" t="n">
+      <c r="V63" t="n">
         <v>7548</v>
       </c>
-      <c r="W63" s="14" t="n">
+      <c r="W63" t="n">
         <v>4824</v>
       </c>
-      <c r="X63" s="14" t="n">
+      <c r="X63" t="n">
         <v>3446</v>
       </c>
-      <c r="Y63" s="14" t="n">
+      <c r="Y63" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -81,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -101,11 +101,17 @@
     <border>
       <left style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,6 +153,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -514,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y64"/>
+  <dimension ref="A1:Y66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5809,6 +5827,164 @@
         <v>3600</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="n">
+        <v>5067</v>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>8954</v>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>4005</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>8097</v>
+      </c>
+      <c r="F65" s="16" t="n">
+        <v>4866</v>
+      </c>
+      <c r="G65" s="16" t="n">
+        <v>4508</v>
+      </c>
+      <c r="H65" s="16" t="n">
+        <v>7926</v>
+      </c>
+      <c r="I65" s="16" t="n">
+        <v>7824</v>
+      </c>
+      <c r="J65" s="16" t="n">
+        <v>3555</v>
+      </c>
+      <c r="K65" s="16" t="n">
+        <v>8382</v>
+      </c>
+      <c r="L65" s="16" t="n">
+        <v>3268</v>
+      </c>
+      <c r="M65" s="16" t="n">
+        <v>8510</v>
+      </c>
+      <c r="N65" s="16" t="n">
+        <v>3720</v>
+      </c>
+      <c r="O65" s="16" t="n">
+        <v>8251</v>
+      </c>
+      <c r="P65" s="16" t="n">
+        <v>2886</v>
+      </c>
+      <c r="Q65" s="16" t="n">
+        <v>2383</v>
+      </c>
+      <c r="R65" s="16" t="n">
+        <v>8305</v>
+      </c>
+      <c r="S65" s="16" t="n">
+        <v>4004</v>
+      </c>
+      <c r="T65" s="16" t="n">
+        <v>5313</v>
+      </c>
+      <c r="U65" s="16" t="n">
+        <v>5361</v>
+      </c>
+      <c r="V65" s="16" t="n">
+        <v>7875</v>
+      </c>
+      <c r="W65" s="16" t="n">
+        <v>5265</v>
+      </c>
+      <c r="X65" s="16" t="n">
+        <v>3579</v>
+      </c>
+      <c r="Y65" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="n">
+        <v>4911</v>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>8152</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>4057</v>
+      </c>
+      <c r="E66" s="18" t="n">
+        <v>8117</v>
+      </c>
+      <c r="F66" s="18" t="n">
+        <v>4912</v>
+      </c>
+      <c r="G66" s="18" t="n">
+        <v>4562</v>
+      </c>
+      <c r="H66" s="18" t="n">
+        <v>8458</v>
+      </c>
+      <c r="I66" s="18" t="n">
+        <v>8216</v>
+      </c>
+      <c r="J66" s="18" t="n">
+        <v>3568</v>
+      </c>
+      <c r="K66" s="18" t="n">
+        <v>8645</v>
+      </c>
+      <c r="L66" s="18" t="n">
+        <v>3108</v>
+      </c>
+      <c r="M66" s="18" t="n">
+        <v>7899</v>
+      </c>
+      <c r="N66" s="18" t="n">
+        <v>3545</v>
+      </c>
+      <c r="O66" s="18" t="n">
+        <v>7979</v>
+      </c>
+      <c r="P66" s="18" t="n">
+        <v>3005</v>
+      </c>
+      <c r="Q66" s="18" t="n">
+        <v>2409</v>
+      </c>
+      <c r="R66" s="18" t="n">
+        <v>8646</v>
+      </c>
+      <c r="S66" s="18" t="n">
+        <v>3807</v>
+      </c>
+      <c r="T66" s="18" t="n">
+        <v>5542</v>
+      </c>
+      <c r="U66" s="18" t="n">
+        <v>5600</v>
+      </c>
+      <c r="V66" s="18" t="n">
+        <v>8011</v>
+      </c>
+      <c r="W66" s="18" t="n">
+        <v>5417</v>
+      </c>
+      <c r="X66" s="18" t="n">
+        <v>3653</v>
+      </c>
+      <c r="Y66" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -81,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -107,11 +107,14 @@
     <border>
       <left style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -165,6 +168,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -532,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y66"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5828,160 +5837,239 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="15" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B65" s="16" t="n">
+      <c r="B65" t="n">
         <v>5067</v>
       </c>
-      <c r="C65" s="16" t="n">
+      <c r="C65" t="n">
         <v>8954</v>
       </c>
-      <c r="D65" s="16" t="n">
+      <c r="D65" t="n">
         <v>4005</v>
       </c>
-      <c r="E65" s="16" t="n">
+      <c r="E65" t="n">
         <v>8097</v>
       </c>
-      <c r="F65" s="16" t="n">
+      <c r="F65" t="n">
         <v>4866</v>
       </c>
-      <c r="G65" s="16" t="n">
+      <c r="G65" t="n">
         <v>4508</v>
       </c>
-      <c r="H65" s="16" t="n">
+      <c r="H65" t="n">
         <v>7926</v>
       </c>
-      <c r="I65" s="16" t="n">
+      <c r="I65" t="n">
         <v>7824</v>
       </c>
-      <c r="J65" s="16" t="n">
+      <c r="J65" t="n">
         <v>3555</v>
       </c>
-      <c r="K65" s="16" t="n">
+      <c r="K65" t="n">
         <v>8382</v>
       </c>
-      <c r="L65" s="16" t="n">
+      <c r="L65" t="n">
         <v>3268</v>
       </c>
-      <c r="M65" s="16" t="n">
+      <c r="M65" t="n">
         <v>8510</v>
       </c>
-      <c r="N65" s="16" t="n">
+      <c r="N65" t="n">
         <v>3720</v>
       </c>
-      <c r="O65" s="16" t="n">
+      <c r="O65" t="n">
         <v>8251</v>
       </c>
-      <c r="P65" s="16" t="n">
+      <c r="P65" t="n">
         <v>2886</v>
       </c>
-      <c r="Q65" s="16" t="n">
+      <c r="Q65" t="n">
         <v>2383</v>
       </c>
-      <c r="R65" s="16" t="n">
+      <c r="R65" t="n">
         <v>8305</v>
       </c>
-      <c r="S65" s="16" t="n">
+      <c r="S65" t="n">
         <v>4004</v>
       </c>
-      <c r="T65" s="16" t="n">
+      <c r="T65" t="n">
         <v>5313</v>
       </c>
-      <c r="U65" s="16" t="n">
+      <c r="U65" t="n">
         <v>5361</v>
       </c>
-      <c r="V65" s="16" t="n">
+      <c r="V65" t="n">
         <v>7875</v>
       </c>
-      <c r="W65" s="16" t="n">
+      <c r="W65" t="n">
         <v>5265</v>
       </c>
-      <c r="X65" s="16" t="n">
+      <c r="X65" t="n">
         <v>3579</v>
       </c>
-      <c r="Y65" s="16" t="n">
+      <c r="Y65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B66" s="18" t="n">
+      <c r="B66" t="n">
         <v>4911</v>
       </c>
-      <c r="C66" s="18" t="n">
+      <c r="C66" t="n">
         <v>8152</v>
       </c>
-      <c r="D66" s="18" t="n">
+      <c r="D66" t="n">
         <v>4057</v>
       </c>
-      <c r="E66" s="18" t="n">
+      <c r="E66" t="n">
         <v>8117</v>
       </c>
-      <c r="F66" s="18" t="n">
+      <c r="F66" t="n">
         <v>4912</v>
       </c>
-      <c r="G66" s="18" t="n">
+      <c r="G66" t="n">
         <v>4562</v>
       </c>
-      <c r="H66" s="18" t="n">
+      <c r="H66" t="n">
         <v>8458</v>
       </c>
-      <c r="I66" s="18" t="n">
+      <c r="I66" t="n">
         <v>8216</v>
       </c>
-      <c r="J66" s="18" t="n">
+      <c r="J66" t="n">
         <v>3568</v>
       </c>
-      <c r="K66" s="18" t="n">
+      <c r="K66" t="n">
         <v>8645</v>
       </c>
-      <c r="L66" s="18" t="n">
+      <c r="L66" t="n">
         <v>3108</v>
       </c>
-      <c r="M66" s="18" t="n">
+      <c r="M66" t="n">
         <v>7899</v>
       </c>
-      <c r="N66" s="18" t="n">
+      <c r="N66" t="n">
         <v>3545</v>
       </c>
-      <c r="O66" s="18" t="n">
+      <c r="O66" t="n">
         <v>7979</v>
       </c>
-      <c r="P66" s="18" t="n">
+      <c r="P66" t="n">
         <v>3005</v>
       </c>
-      <c r="Q66" s="18" t="n">
+      <c r="Q66" t="n">
         <v>2409</v>
       </c>
-      <c r="R66" s="18" t="n">
+      <c r="R66" t="n">
         <v>8646</v>
       </c>
-      <c r="S66" s="18" t="n">
+      <c r="S66" t="n">
         <v>3807</v>
       </c>
-      <c r="T66" s="18" t="n">
+      <c r="T66" t="n">
         <v>5542</v>
       </c>
-      <c r="U66" s="18" t="n">
+      <c r="U66" t="n">
         <v>5600</v>
       </c>
-      <c r="V66" s="18" t="n">
+      <c r="V66" t="n">
         <v>8011</v>
       </c>
-      <c r="W66" s="18" t="n">
+      <c r="W66" t="n">
         <v>5417</v>
       </c>
-      <c r="X66" s="18" t="n">
+      <c r="X66" t="n">
         <v>3653</v>
       </c>
-      <c r="Y66" s="18" t="n">
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4722</v>
+      </c>
+      <c r="C67" t="n">
+        <v>8984</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3782</v>
+      </c>
+      <c r="E67" t="n">
+        <v>7956</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4790</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4463</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7617</v>
+      </c>
+      <c r="I67" t="n">
+        <v>7850</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3574</v>
+      </c>
+      <c r="K67" t="n">
+        <v>8578</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3217</v>
+      </c>
+      <c r="M67" t="n">
+        <v>8328</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3674</v>
+      </c>
+      <c r="O67" t="n">
+        <v>7668</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2990</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2397</v>
+      </c>
+      <c r="R67" t="n">
+        <v>8870</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3827</v>
+      </c>
+      <c r="T67" t="n">
+        <v>5502</v>
+      </c>
+      <c r="U67" t="n">
+        <v>5791</v>
+      </c>
+      <c r="V67" t="n">
+        <v>8167</v>
+      </c>
+      <c r="W67" t="n">
+        <v>5244</v>
+      </c>
+      <c r="X67" t="n">
+        <v>3475</v>
+      </c>
+      <c r="Y67" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -81,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -110,11 +110,14 @@
     <border>
       <left style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -174,6 +177,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -541,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y67"/>
+  <dimension ref="A1:Y68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6073,6 +6082,85 @@
         <v>0</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="n">
+        <v>4621</v>
+      </c>
+      <c r="C68" s="22" t="n">
+        <v>9205</v>
+      </c>
+      <c r="D68" s="22" t="n">
+        <v>3907</v>
+      </c>
+      <c r="E68" s="22" t="n">
+        <v>7770</v>
+      </c>
+      <c r="F68" s="22" t="n">
+        <v>4774</v>
+      </c>
+      <c r="G68" s="22" t="n">
+        <v>4407</v>
+      </c>
+      <c r="H68" s="22" t="n">
+        <v>7876</v>
+      </c>
+      <c r="I68" s="22" t="n">
+        <v>7624</v>
+      </c>
+      <c r="J68" s="22" t="n">
+        <v>3535</v>
+      </c>
+      <c r="K68" s="22" t="n">
+        <v>9312</v>
+      </c>
+      <c r="L68" s="22" t="n">
+        <v>3176</v>
+      </c>
+      <c r="M68" s="22" t="n">
+        <v>9062</v>
+      </c>
+      <c r="N68" s="22" t="n">
+        <v>3538</v>
+      </c>
+      <c r="O68" s="22" t="n">
+        <v>7586</v>
+      </c>
+      <c r="P68" s="22" t="n">
+        <v>3124</v>
+      </c>
+      <c r="Q68" s="22" t="n">
+        <v>2380</v>
+      </c>
+      <c r="R68" s="22" t="n">
+        <v>9086</v>
+      </c>
+      <c r="S68" s="22" t="n">
+        <v>3663</v>
+      </c>
+      <c r="T68" s="22" t="n">
+        <v>5718</v>
+      </c>
+      <c r="U68" s="22" t="n">
+        <v>6069</v>
+      </c>
+      <c r="V68" s="22" t="n">
+        <v>8195</v>
+      </c>
+      <c r="W68" s="22" t="n">
+        <v>5203</v>
+      </c>
+      <c r="X68" s="22" t="n">
+        <v>3460</v>
+      </c>
+      <c r="Y68" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -6083,81 +6083,81 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="21" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="B68" s="22" t="n">
+      <c r="B68" t="n">
         <v>4621</v>
       </c>
-      <c r="C68" s="22" t="n">
+      <c r="C68" t="n">
         <v>9205</v>
       </c>
-      <c r="D68" s="22" t="n">
+      <c r="D68" t="n">
         <v>3907</v>
       </c>
-      <c r="E68" s="22" t="n">
+      <c r="E68" t="n">
         <v>7770</v>
       </c>
-      <c r="F68" s="22" t="n">
+      <c r="F68" t="n">
         <v>4774</v>
       </c>
-      <c r="G68" s="22" t="n">
+      <c r="G68" t="n">
         <v>4407</v>
       </c>
-      <c r="H68" s="22" t="n">
+      <c r="H68" t="n">
         <v>7876</v>
       </c>
-      <c r="I68" s="22" t="n">
+      <c r="I68" t="n">
         <v>7624</v>
       </c>
-      <c r="J68" s="22" t="n">
+      <c r="J68" t="n">
         <v>3535</v>
       </c>
-      <c r="K68" s="22" t="n">
+      <c r="K68" t="n">
         <v>9312</v>
       </c>
-      <c r="L68" s="22" t="n">
+      <c r="L68" t="n">
         <v>3176</v>
       </c>
-      <c r="M68" s="22" t="n">
+      <c r="M68" t="n">
         <v>9062</v>
       </c>
-      <c r="N68" s="22" t="n">
+      <c r="N68" t="n">
         <v>3538</v>
       </c>
-      <c r="O68" s="22" t="n">
+      <c r="O68" t="n">
         <v>7586</v>
       </c>
-      <c r="P68" s="22" t="n">
+      <c r="P68" t="n">
         <v>3124</v>
       </c>
-      <c r="Q68" s="22" t="n">
+      <c r="Q68" t="n">
         <v>2380</v>
       </c>
-      <c r="R68" s="22" t="n">
+      <c r="R68" t="n">
         <v>9086</v>
       </c>
-      <c r="S68" s="22" t="n">
+      <c r="S68" t="n">
         <v>3663</v>
       </c>
-      <c r="T68" s="22" t="n">
+      <c r="T68" t="n">
         <v>5718</v>
       </c>
-      <c r="U68" s="22" t="n">
+      <c r="U68" t="n">
         <v>6069</v>
       </c>
-      <c r="V68" s="22" t="n">
+      <c r="V68" t="n">
         <v>8195</v>
       </c>
-      <c r="W68" s="22" t="n">
+      <c r="W68" t="n">
         <v>5203</v>
       </c>
-      <c r="X68" s="22" t="n">
+      <c r="X68" t="n">
         <v>3460</v>
       </c>
-      <c r="Y68" s="22" t="n">
+      <c r="Y68" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -81,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -113,11 +113,17 @@
     <border>
       <left style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -183,6 +189,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -550,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y68"/>
+  <dimension ref="A1:Y70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6161,6 +6179,164 @@
         <v>0</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4588</v>
+      </c>
+      <c r="C69" t="n">
+        <v>9222</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3740</v>
+      </c>
+      <c r="E69" t="n">
+        <v>7456</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4562</v>
+      </c>
+      <c r="G69" t="n">
+        <v>4557</v>
+      </c>
+      <c r="H69" t="n">
+        <v>7445</v>
+      </c>
+      <c r="I69" t="n">
+        <v>7449</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3580</v>
+      </c>
+      <c r="K69" t="n">
+        <v>9234</v>
+      </c>
+      <c r="L69" t="n">
+        <v>3023</v>
+      </c>
+      <c r="M69" t="n">
+        <v>9083</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3497</v>
+      </c>
+      <c r="O69" t="n">
+        <v>7731</v>
+      </c>
+      <c r="P69" t="n">
+        <v>3097</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2356</v>
+      </c>
+      <c r="R69" t="n">
+        <v>8697</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3838</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5917</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5878</v>
+      </c>
+      <c r="V69" t="n">
+        <v>8226</v>
+      </c>
+      <c r="W69" t="n">
+        <v>5120</v>
+      </c>
+      <c r="X69" t="n">
+        <v>3508</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B70" s="26" t="n">
+        <v>4741</v>
+      </c>
+      <c r="C70" s="26" t="n">
+        <v>9090</v>
+      </c>
+      <c r="D70" s="26" t="n">
+        <v>3721</v>
+      </c>
+      <c r="E70" s="26" t="n">
+        <v>7699</v>
+      </c>
+      <c r="F70" s="26" t="n">
+        <v>4501</v>
+      </c>
+      <c r="G70" s="26" t="n">
+        <v>4633</v>
+      </c>
+      <c r="H70" s="26" t="n">
+        <v>7607</v>
+      </c>
+      <c r="I70" s="26" t="n">
+        <v>7591</v>
+      </c>
+      <c r="J70" s="26" t="n">
+        <v>3601</v>
+      </c>
+      <c r="K70" s="26" t="n">
+        <v>8372</v>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>3075</v>
+      </c>
+      <c r="M70" s="26" t="n">
+        <v>9023</v>
+      </c>
+      <c r="N70" s="26" t="n">
+        <v>3374</v>
+      </c>
+      <c r="O70" s="26" t="n">
+        <v>7581</v>
+      </c>
+      <c r="P70" s="26" t="n">
+        <v>3156</v>
+      </c>
+      <c r="Q70" s="26" t="n">
+        <v>2310</v>
+      </c>
+      <c r="R70" s="26" t="n">
+        <v>8647</v>
+      </c>
+      <c r="S70" s="26" t="n">
+        <v>3692</v>
+      </c>
+      <c r="T70" s="26" t="n">
+        <v>5772</v>
+      </c>
+      <c r="U70" s="26" t="n">
+        <v>5751</v>
+      </c>
+      <c r="V70" s="26" t="n">
+        <v>8259</v>
+      </c>
+      <c r="W70" s="26" t="n">
+        <v>5109</v>
+      </c>
+      <c r="X70" s="26" t="n">
+        <v>3555</v>
+      </c>
+      <c r="Y70" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -81,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -119,11 +119,14 @@
     <border>
       <left style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -201,6 +204,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -568,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y70"/>
+  <dimension ref="A1:Y71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6259,81 +6268,160 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="25" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B70" s="26" t="n">
+      <c r="B70" t="n">
         <v>4741</v>
       </c>
-      <c r="C70" s="26" t="n">
+      <c r="C70" t="n">
         <v>9090</v>
       </c>
-      <c r="D70" s="26" t="n">
+      <c r="D70" t="n">
         <v>3721</v>
       </c>
-      <c r="E70" s="26" t="n">
+      <c r="E70" t="n">
         <v>7699</v>
       </c>
-      <c r="F70" s="26" t="n">
+      <c r="F70" t="n">
         <v>4501</v>
       </c>
-      <c r="G70" s="26" t="n">
+      <c r="G70" t="n">
         <v>4633</v>
       </c>
-      <c r="H70" s="26" t="n">
+      <c r="H70" t="n">
         <v>7607</v>
       </c>
-      <c r="I70" s="26" t="n">
+      <c r="I70" t="n">
         <v>7591</v>
       </c>
-      <c r="J70" s="26" t="n">
+      <c r="J70" t="n">
         <v>3601</v>
       </c>
-      <c r="K70" s="26" t="n">
+      <c r="K70" t="n">
         <v>8372</v>
       </c>
-      <c r="L70" s="26" t="n">
+      <c r="L70" t="n">
         <v>3075</v>
       </c>
-      <c r="M70" s="26" t="n">
+      <c r="M70" t="n">
         <v>9023</v>
       </c>
-      <c r="N70" s="26" t="n">
+      <c r="N70" t="n">
         <v>3374</v>
       </c>
-      <c r="O70" s="26" t="n">
+      <c r="O70" t="n">
         <v>7581</v>
       </c>
-      <c r="P70" s="26" t="n">
+      <c r="P70" t="n">
         <v>3156</v>
       </c>
-      <c r="Q70" s="26" t="n">
+      <c r="Q70" t="n">
         <v>2310</v>
       </c>
-      <c r="R70" s="26" t="n">
+      <c r="R70" t="n">
         <v>8647</v>
       </c>
-      <c r="S70" s="26" t="n">
+      <c r="S70" t="n">
         <v>3692</v>
       </c>
-      <c r="T70" s="26" t="n">
+      <c r="T70" t="n">
         <v>5772</v>
       </c>
-      <c r="U70" s="26" t="n">
+      <c r="U70" t="n">
         <v>5751</v>
       </c>
-      <c r="V70" s="26" t="n">
+      <c r="V70" t="n">
         <v>8259</v>
       </c>
-      <c r="W70" s="26" t="n">
+      <c r="W70" t="n">
         <v>5109</v>
       </c>
-      <c r="X70" s="26" t="n">
+      <c r="X70" t="n">
         <v>3555</v>
       </c>
-      <c r="Y70" s="26" t="n">
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B71" s="28" t="n">
+        <v>4737</v>
+      </c>
+      <c r="C71" s="28" t="n">
+        <v>8599</v>
+      </c>
+      <c r="D71" s="28" t="n">
+        <v>3817</v>
+      </c>
+      <c r="E71" s="28" t="n">
+        <v>7505</v>
+      </c>
+      <c r="F71" s="28" t="n">
+        <v>4345</v>
+      </c>
+      <c r="G71" s="28" t="n">
+        <v>4688</v>
+      </c>
+      <c r="H71" s="28" t="n">
+        <v>7728</v>
+      </c>
+      <c r="I71" s="28" t="n">
+        <v>7767</v>
+      </c>
+      <c r="J71" s="28" t="n">
+        <v>3567</v>
+      </c>
+      <c r="K71" s="28" t="n">
+        <v>8517</v>
+      </c>
+      <c r="L71" s="28" t="n">
+        <v>2974</v>
+      </c>
+      <c r="M71" s="28" t="n">
+        <v>8868</v>
+      </c>
+      <c r="N71" s="28" t="n">
+        <v>3398</v>
+      </c>
+      <c r="O71" s="28" t="n">
+        <v>7592</v>
+      </c>
+      <c r="P71" s="28" t="n">
+        <v>3072</v>
+      </c>
+      <c r="Q71" s="28" t="n">
+        <v>2390</v>
+      </c>
+      <c r="R71" s="28" t="n">
+        <v>8554</v>
+      </c>
+      <c r="S71" s="28" t="n">
+        <v>3624</v>
+      </c>
+      <c r="T71" s="28" t="n">
+        <v>5724</v>
+      </c>
+      <c r="U71" s="28" t="n">
+        <v>5876</v>
+      </c>
+      <c r="V71" s="28" t="n">
+        <v>7849</v>
+      </c>
+      <c r="W71" s="28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="X71" s="28" t="n">
+        <v>3597</v>
+      </c>
+      <c r="Y71" s="28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -81,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -122,11 +122,14 @@
     <border>
       <left style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -210,6 +213,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y71"/>
+  <dimension ref="A1:Y72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6347,81 +6356,160 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="27" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B71" s="28" t="n">
+      <c r="B71" t="n">
         <v>4737</v>
       </c>
-      <c r="C71" s="28" t="n">
+      <c r="C71" t="n">
         <v>8599</v>
       </c>
-      <c r="D71" s="28" t="n">
+      <c r="D71" t="n">
         <v>3817</v>
       </c>
-      <c r="E71" s="28" t="n">
+      <c r="E71" t="n">
         <v>7505</v>
       </c>
-      <c r="F71" s="28" t="n">
+      <c r="F71" t="n">
         <v>4345</v>
       </c>
-      <c r="G71" s="28" t="n">
+      <c r="G71" t="n">
         <v>4688</v>
       </c>
-      <c r="H71" s="28" t="n">
+      <c r="H71" t="n">
         <v>7728</v>
       </c>
-      <c r="I71" s="28" t="n">
+      <c r="I71" t="n">
         <v>7767</v>
       </c>
-      <c r="J71" s="28" t="n">
+      <c r="J71" t="n">
         <v>3567</v>
       </c>
-      <c r="K71" s="28" t="n">
+      <c r="K71" t="n">
         <v>8517</v>
       </c>
-      <c r="L71" s="28" t="n">
+      <c r="L71" t="n">
         <v>2974</v>
       </c>
-      <c r="M71" s="28" t="n">
+      <c r="M71" t="n">
         <v>8868</v>
       </c>
-      <c r="N71" s="28" t="n">
+      <c r="N71" t="n">
         <v>3398</v>
       </c>
-      <c r="O71" s="28" t="n">
+      <c r="O71" t="n">
         <v>7592</v>
       </c>
-      <c r="P71" s="28" t="n">
+      <c r="P71" t="n">
         <v>3072</v>
       </c>
-      <c r="Q71" s="28" t="n">
+      <c r="Q71" t="n">
         <v>2390</v>
       </c>
-      <c r="R71" s="28" t="n">
+      <c r="R71" t="n">
         <v>8554</v>
       </c>
-      <c r="S71" s="28" t="n">
+      <c r="S71" t="n">
         <v>3624</v>
       </c>
-      <c r="T71" s="28" t="n">
+      <c r="T71" t="n">
         <v>5724</v>
       </c>
-      <c r="U71" s="28" t="n">
+      <c r="U71" t="n">
         <v>5876</v>
       </c>
-      <c r="V71" s="28" t="n">
+      <c r="V71" t="n">
         <v>7849</v>
       </c>
-      <c r="W71" s="28" t="n">
+      <c r="W71" t="n">
         <v>5000</v>
       </c>
-      <c r="X71" s="28" t="n">
+      <c r="X71" t="n">
         <v>3597</v>
       </c>
-      <c r="Y71" s="28" t="n">
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B72" s="30" t="n">
+        <v>4569</v>
+      </c>
+      <c r="C72" s="30" t="n">
+        <v>8758</v>
+      </c>
+      <c r="D72" s="30" t="n">
+        <v>3791</v>
+      </c>
+      <c r="E72" s="30" t="n">
+        <v>7723</v>
+      </c>
+      <c r="F72" s="30" t="n">
+        <v>4455</v>
+      </c>
+      <c r="G72" s="30" t="n">
+        <v>4580</v>
+      </c>
+      <c r="H72" s="30" t="n">
+        <v>7626</v>
+      </c>
+      <c r="I72" s="30" t="n">
+        <v>7221</v>
+      </c>
+      <c r="J72" s="30" t="n">
+        <v>3455</v>
+      </c>
+      <c r="K72" s="30" t="n">
+        <v>8468</v>
+      </c>
+      <c r="L72" s="30" t="n">
+        <v>2892</v>
+      </c>
+      <c r="M72" s="30" t="n">
+        <v>8127</v>
+      </c>
+      <c r="N72" s="30" t="n">
+        <v>3285</v>
+      </c>
+      <c r="O72" s="30" t="n">
+        <v>7401</v>
+      </c>
+      <c r="P72" s="30" t="n">
+        <v>3115</v>
+      </c>
+      <c r="Q72" s="30" t="n">
+        <v>2418</v>
+      </c>
+      <c r="R72" s="30" t="n">
+        <v>8906</v>
+      </c>
+      <c r="S72" s="30" t="n">
+        <v>3448</v>
+      </c>
+      <c r="T72" s="30" t="n">
+        <v>5446</v>
+      </c>
+      <c r="U72" s="30" t="n">
+        <v>5909</v>
+      </c>
+      <c r="V72" s="30" t="n">
+        <v>7532</v>
+      </c>
+      <c r="W72" s="30" t="n">
+        <v>5122</v>
+      </c>
+      <c r="X72" s="30" t="n">
+        <v>3493</v>
+      </c>
+      <c r="Y72" s="30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y72"/>
+  <dimension ref="A1:Y73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6435,82 +6435,158 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B72" s="30" t="n">
+      <c r="B72" t="n">
         <v>4569</v>
       </c>
-      <c r="C72" s="30" t="n">
+      <c r="C72" t="n">
         <v>8758</v>
       </c>
-      <c r="D72" s="30" t="n">
+      <c r="D72" t="n">
         <v>3791</v>
       </c>
-      <c r="E72" s="30" t="n">
+      <c r="E72" t="n">
         <v>7723</v>
       </c>
-      <c r="F72" s="30" t="n">
+      <c r="F72" t="n">
         <v>4455</v>
       </c>
-      <c r="G72" s="30" t="n">
+      <c r="G72" t="n">
         <v>4580</v>
       </c>
-      <c r="H72" s="30" t="n">
+      <c r="H72" t="n">
         <v>7626</v>
       </c>
-      <c r="I72" s="30" t="n">
+      <c r="I72" t="n">
         <v>7221</v>
       </c>
-      <c r="J72" s="30" t="n">
+      <c r="J72" t="n">
         <v>3455</v>
       </c>
-      <c r="K72" s="30" t="n">
+      <c r="K72" t="n">
         <v>8468</v>
       </c>
-      <c r="L72" s="30" t="n">
+      <c r="L72" t="n">
         <v>2892</v>
       </c>
-      <c r="M72" s="30" t="n">
+      <c r="M72" t="n">
         <v>8127</v>
       </c>
-      <c r="N72" s="30" t="n">
+      <c r="N72" t="n">
         <v>3285</v>
       </c>
-      <c r="O72" s="30" t="n">
+      <c r="O72" t="n">
         <v>7401</v>
       </c>
-      <c r="P72" s="30" t="n">
+      <c r="P72" t="n">
         <v>3115</v>
       </c>
-      <c r="Q72" s="30" t="n">
+      <c r="Q72" t="n">
         <v>2418</v>
       </c>
-      <c r="R72" s="30" t="n">
+      <c r="R72" t="n">
         <v>8906</v>
       </c>
-      <c r="S72" s="30" t="n">
+      <c r="S72" t="n">
         <v>3448</v>
       </c>
-      <c r="T72" s="30" t="n">
+      <c r="T72" t="n">
         <v>5446</v>
       </c>
-      <c r="U72" s="30" t="n">
+      <c r="U72" t="n">
         <v>5909</v>
       </c>
-      <c r="V72" s="30" t="n">
+      <c r="V72" t="n">
         <v>7532</v>
       </c>
-      <c r="W72" s="30" t="n">
+      <c r="W72" t="n">
         <v>5122</v>
       </c>
-      <c r="X72" s="30" t="n">
+      <c r="X72" t="n">
         <v>3493</v>
       </c>
-      <c r="Y72" s="30" t="n">
+      <c r="Y72" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C73" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E73" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4600</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H73" t="n">
+        <v>7800</v>
+      </c>
+      <c r="I73" t="n">
+        <v>7700</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K73" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L73" t="n">
+        <v>3100</v>
+      </c>
+      <c r="M73" t="n">
+        <v>8600</v>
+      </c>
+      <c r="N73" t="n">
+        <v>3500</v>
+      </c>
+      <c r="O73" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P73" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R73" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T73" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U73" t="n">
+        <v>5800</v>
+      </c>
+      <c r="V73" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W73" t="n">
+        <v>5200</v>
+      </c>
+      <c r="X73" t="n">
+        <v>3500</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y73"/>
+  <dimension ref="A1:Y76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6589,6 +6589,234 @@
         <v>3500</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C74" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F74" t="n">
+        <v>4600</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H74" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I74" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K74" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L74" t="n">
+        <v>3100</v>
+      </c>
+      <c r="M74" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3500</v>
+      </c>
+      <c r="O74" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P74" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R74" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T74" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U74" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V74" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W74" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X74" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C75" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H75" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I75" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K75" t="n">
+        <v>8800</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M75" t="n">
+        <v>8800</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O75" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P75" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R75" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S75" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T75" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U75" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V75" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W75" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C76" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E76" t="n">
+        <v>7600</v>
+      </c>
+      <c r="F76" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G76" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H76" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I76" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J76" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K76" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L76" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M76" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N76" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O76" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P76" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R76" t="n">
+        <v>8700</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T76" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U76" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V76" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W76" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X76" t="n">
+        <v>3500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y76"/>
+  <dimension ref="A1:Y78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6817,6 +6817,158 @@
         <v>3500</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C77" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E77" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I77" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K77" t="n">
+        <v>8600</v>
+      </c>
+      <c r="L77" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M77" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O77" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P77" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R77" t="n">
+        <v>8700</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T77" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U77" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V77" t="n">
+        <v>7900</v>
+      </c>
+      <c r="W77" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X77" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E78" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H78" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I78" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J78" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K78" t="n">
+        <v>8600</v>
+      </c>
+      <c r="L78" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M78" t="n">
+        <v>8600</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O78" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P78" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R78" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T78" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U78" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V78" t="n">
+        <v>7900</v>
+      </c>
+      <c r="W78" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X78" t="n">
+        <v>3500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/harga_pakan_ternak.xlsx
+++ b/data/harga_pakan_ternak.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y78"/>
+  <dimension ref="A1:Y86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6969,6 +6969,614 @@
         <v>3500</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C79" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D79" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E79" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H79" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I79" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K79" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L79" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M79" t="n">
+        <v>8600</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O79" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R79" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T79" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U79" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V79" t="n">
+        <v>7900</v>
+      </c>
+      <c r="W79" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X79" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C80" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E80" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H80" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I80" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J80" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K80" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L80" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M80" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O80" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P80" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R80" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S80" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T80" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U80" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V80" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W80" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X80" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C81" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F81" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H81" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I81" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J81" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K81" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L81" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M81" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O81" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P81" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R81" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S81" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T81" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U81" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V81" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W81" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X81" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C82" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E82" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G82" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H82" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I82" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K82" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L82" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M82" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O82" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P82" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R82" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S82" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T82" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U82" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V82" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W82" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X82" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C83" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E83" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G83" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H83" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I83" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J83" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K83" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L83" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M83" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N83" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O83" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P83" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R83" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T83" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U83" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V83" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W83" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X83" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C84" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E84" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G84" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H84" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I84" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J84" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K84" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L84" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M84" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N84" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O84" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P84" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R84" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T84" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U84" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V84" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W84" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X84" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C85" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E85" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H85" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I85" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K85" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L85" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M85" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O85" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P85" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R85" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T85" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U85" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V85" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W85" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X85" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C86" t="n">
+        <v>8900</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E86" t="n">
+        <v>7700</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H86" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I86" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J86" t="n">
+        <v>3600</v>
+      </c>
+      <c r="K86" t="n">
+        <v>8700</v>
+      </c>
+      <c r="L86" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M86" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3400</v>
+      </c>
+      <c r="O86" t="n">
+        <v>7600</v>
+      </c>
+      <c r="P86" t="n">
+        <v>3100</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R86" t="n">
+        <v>8800</v>
+      </c>
+      <c r="S86" t="n">
+        <v>3700</v>
+      </c>
+      <c r="T86" t="n">
+        <v>5700</v>
+      </c>
+      <c r="U86" t="n">
+        <v>5900</v>
+      </c>
+      <c r="V86" t="n">
+        <v>8000</v>
+      </c>
+      <c r="W86" t="n">
+        <v>5100</v>
+      </c>
+      <c r="X86" t="n">
+        <v>3500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
